--- a/物资/资产清单.xlsx
+++ b/物资/资产清单.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产清单" sheetId="1" r:id="Rba07cb89074b4dd8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类汇总" sheetId="2" r:id="Rf64a617ce3d04b8c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="未纳入资产" sheetId="3" r:id="Rb217c97985e24c11"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产清单" sheetId="1" r:id="R278bb2551c7748e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类汇总" sheetId="2" r:id="R459c318a253b45ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="未纳入资产" sheetId="3" r:id="R336099e4b0e94b20"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -21,7 +21,7 @@
     <x:numFmt numFmtId="202" formatCode="yyyy-mm-dd"/>
     <x:numFmt numFmtId="203" formatCode="0"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -90,8 +90,13 @@
       <x:color rgb="FF7C5700"/>
       <x:name val="Microsoft YaHei"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF203040"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="8">
+  <x:fills count="15">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -128,8 +133,43 @@
         <x:fgColor rgb="FFFFF2CC"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="7">
+  <x:borders count="8">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -191,11 +231,16 @@
         <x:color rgb="FF24476B"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="93">
+  <x:cellXfs count="165">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -383,6 +428,208 @@
     <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0"/>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="12" fillId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="12" fillId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="12" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="12" fillId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="12" fillId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="12" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="12" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="12" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="12" fillId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="12" fillId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="12" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="12" fillId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="12" fillId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="12" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="13" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="13" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="13" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="13" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="12" fillId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="12" fillId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="12" fillId="13" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="12" fillId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="12" fillId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="12" fillId="13" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="3" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -391,8 +638,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AssetsTable" displayName="AssetsTable" ref="A6:R63" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A6:R63"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AssetsTable" displayName="AssetsTable" ref="A6:R76" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A6:R76"/>
   <x:tableColumns count="18">
     <x:tableColumn id="1" name="资产编号"/>
     <x:tableColumn id="2" name="管理类别"/>
@@ -683,8 +930,8 @@
       <x:c r="B3" s="19"/>
       <x:c r="C3" s="20"/>
       <x:c r="D3" s="27" t="n">
-        <x:f>COUNTA(A7:A63)</x:f>
-        <x:v>57</x:v>
+        <x:f>COUNTA(A7:A76)</x:f>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E3" s="28"/>
       <x:c r="F3" s="18" t="str">
@@ -693,8 +940,8 @@
       <x:c r="G3" s="19"/>
       <x:c r="H3" s="20"/>
       <x:c r="I3" s="27" t="n">
-        <x:f>SUM(F7:F63)</x:f>
-        <x:v>74</x:v>
+        <x:f>SUM(F7:F76)</x:f>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="J3" s="28"/>
       <x:c r="K3" s="18" t="str">
@@ -703,8 +950,8 @@
       <x:c r="L3" s="19"/>
       <x:c r="M3" s="20"/>
       <x:c r="N3" s="32" t="n">
-        <x:f>SUM(H7:H63)</x:f>
-        <x:v>4144.81</x:v>
+        <x:f>SUM(H7:H76)</x:f>
+        <x:v>6672.69</x:v>
       </x:c>
       <x:c r="O3" s="33"/>
       <x:c r="P3" s="33"/>
@@ -3377,6 +3624,604 @@
       </x:c>
       <x:c r="R63" s="59" t="str">
         <x:v>10条合计4.30元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="34" customHeight="1">
+      <x:c r="A64" s="100" t="str">
+        <x:v>ZC-20260817-001</x:v>
+      </x:c>
+      <x:c r="B64" s="100" t="str">
+        <x:v>材料耗材</x:v>
+      </x:c>
+      <x:c r="C64" s="100" t="str">
+        <x:v>低值易耗品</x:v>
+      </x:c>
+      <x:c r="D64" s="103" t="str">
+        <x:v>美标特软硅胶线</x:v>
+      </x:c>
+      <x:c r="E64" s="103" t="str">
+        <x:v>28AWG / 黑色 / 10米/卷</x:v>
+      </x:c>
+      <x:c r="F64" s="106" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G64" s="112" t="n">
+        <x:v>8.49</x:v>
+      </x:c>
+      <x:c r="H64" s="112" t="n">
+        <x:v>8.49</x:v>
+      </x:c>
+      <x:c r="I64" s="115" t="n">
+        <x:v>46251</x:v>
+      </x:c>
+      <x:c r="J64" s="103" t="str">
+        <x:v>skygod旗舰店</x:v>
+      </x:c>
+      <x:c r="K64" s="100"/>
+      <x:c r="L64" s="100"/>
+      <x:c r="M64" s="100"/>
+      <x:c r="N64" s="100"/>
+      <x:c r="O64" s="100"/>
+      <x:c r="P64" s="109" t="str">
+        <x:v>2026-08-17</x:v>
+      </x:c>
+      <x:c r="Q64" s="109" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="R64" s="103" t="str">
+        <x:v>优惠后价；先用后付</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="34" customHeight="1">
+      <x:c r="A65" s="101" t="str">
+        <x:v>ZC-20260817-002</x:v>
+      </x:c>
+      <x:c r="B65" s="101" t="str">
+        <x:v>材料耗材</x:v>
+      </x:c>
+      <x:c r="C65" s="101" t="str">
+        <x:v>低值易耗品</x:v>
+      </x:c>
+      <x:c r="D65" s="104" t="str">
+        <x:v>美标特软硅胶线</x:v>
+      </x:c>
+      <x:c r="E65" s="104" t="str">
+        <x:v>28AWG / 红色 / 10米/卷</x:v>
+      </x:c>
+      <x:c r="F65" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G65" s="113" t="n">
+        <x:v>8.49</x:v>
+      </x:c>
+      <x:c r="H65" s="113" t="n">
+        <x:v>8.49</x:v>
+      </x:c>
+      <x:c r="I65" s="116" t="n">
+        <x:v>46251</x:v>
+      </x:c>
+      <x:c r="J65" s="104" t="str">
+        <x:v>skygod旗舰店</x:v>
+      </x:c>
+      <x:c r="K65" s="101"/>
+      <x:c r="L65" s="101"/>
+      <x:c r="M65" s="101"/>
+      <x:c r="N65" s="101"/>
+      <x:c r="O65" s="101"/>
+      <x:c r="P65" s="110" t="str">
+        <x:v>2026-08-17</x:v>
+      </x:c>
+      <x:c r="Q65" s="110" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="R65" s="104" t="str">
+        <x:v>优惠后价；先用后付</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="34" customHeight="1">
+      <x:c r="A66" s="100" t="str">
+        <x:v>ZC-20260817-003</x:v>
+      </x:c>
+      <x:c r="B66" s="100" t="str">
+        <x:v>电子元器件</x:v>
+      </x:c>
+      <x:c r="C66" s="100" t="str">
+        <x:v>项目组件</x:v>
+      </x:c>
+      <x:c r="D66" s="103" t="str">
+        <x:v>XT60母对母延长线</x:v>
+      </x:c>
+      <x:c r="E66" s="103" t="str">
+        <x:v>0.2m / XT60母对母 / 10AWG（5.3mm²）</x:v>
+      </x:c>
+      <x:c r="F66" s="106" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G66" s="112" t="n">
+        <x:v>15.88</x:v>
+      </x:c>
+      <x:c r="H66" s="112" t="n">
+        <x:v>15.88</x:v>
+      </x:c>
+      <x:c r="I66" s="115" t="n">
+        <x:v>46251</x:v>
+      </x:c>
+      <x:c r="J66" s="103" t="str">
+        <x:v>安捷达线束</x:v>
+      </x:c>
+      <x:c r="K66" s="100"/>
+      <x:c r="L66" s="100"/>
+      <x:c r="M66" s="100"/>
+      <x:c r="N66" s="100"/>
+      <x:c r="O66" s="100"/>
+      <x:c r="P66" s="109" t="str">
+        <x:v>2026-08-17</x:v>
+      </x:c>
+      <x:c r="Q66" s="109" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="R66" s="103" t="str">
+        <x:v>免密支付；包邮</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="34" customHeight="1">
+      <x:c r="A67" s="102" t="str">
+        <x:v>ZC-20260817-004</x:v>
+      </x:c>
+      <x:c r="B67" s="102" t="str">
+        <x:v>材料耗材</x:v>
+      </x:c>
+      <x:c r="C67" s="102" t="str">
+        <x:v>低值易耗品</x:v>
+      </x:c>
+      <x:c r="D67" s="105" t="str">
+        <x:v>六角铜柱机箱螺丝钉</x:v>
+      </x:c>
+      <x:c r="E67" s="105" t="str">
+        <x:v>M3×20+6 / 20颗</x:v>
+      </x:c>
+      <x:c r="F67" s="108" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G67" s="114" t="n">
+        <x:v>5.66</x:v>
+      </x:c>
+      <x:c r="H67" s="114" t="n">
+        <x:v>5.66</x:v>
+      </x:c>
+      <x:c r="I67" s="117" t="n">
+        <x:v>46251</x:v>
+      </x:c>
+      <x:c r="J67" s="105" t="str">
+        <x:v>固万基官方旗舰店</x:v>
+      </x:c>
+      <x:c r="K67" s="102"/>
+      <x:c r="L67" s="102"/>
+      <x:c r="M67" s="102"/>
+      <x:c r="N67" s="102"/>
+      <x:c r="O67" s="102"/>
+      <x:c r="P67" s="111" t="str">
+        <x:v>2026-08-17</x:v>
+      </x:c>
+      <x:c r="Q67" s="111" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="R67" s="105" t="str">
+        <x:v>优惠后价；先用后付</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="40" customHeight="1">
+      <x:c r="A68" s="122" t="str">
+        <x:v>ZC-20260817-005</x:v>
+      </x:c>
+      <x:c r="B68" s="122" t="str">
+        <x:v>材料耗材</x:v>
+      </x:c>
+      <x:c r="C68" s="122" t="str">
+        <x:v>低值易耗品</x:v>
+      </x:c>
+      <x:c r="D68" s="123" t="str">
+        <x:v>304不锈钢杯头内六角螺钉</x:v>
+      </x:c>
+      <x:c r="E68" s="123" t="str">
+        <x:v>M3×16 / 100个</x:v>
+      </x:c>
+      <x:c r="F68" s="124" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G68" s="126" t="n">
+        <x:v>3.63</x:v>
+      </x:c>
+      <x:c r="H68" s="126" t="n">
+        <x:v>3.63</x:v>
+      </x:c>
+      <x:c r="I68" s="127" t="n">
+        <x:v>46251</x:v>
+      </x:c>
+      <x:c r="J68" s="123" t="str">
+        <x:v>楚卫旗舰店</x:v>
+      </x:c>
+      <x:c r="K68" s="122"/>
+      <x:c r="L68" s="122"/>
+      <x:c r="M68" s="122"/>
+      <x:c r="N68" s="122"/>
+      <x:c r="O68" s="122"/>
+      <x:c r="P68" s="125" t="str">
+        <x:v>2026-08-17</x:v>
+      </x:c>
+      <x:c r="Q68" s="125" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="R68" s="123" t="str">
+        <x:v>先用后付；当前实付0元，预计自动扣款3.63元；订单号3316977480159071850</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="42" customHeight="1">
+      <x:c r="A69" s="128" t="str">
+        <x:v>ZC-20260818-001</x:v>
+      </x:c>
+      <x:c r="B69" s="128" t="str">
+        <x:v>材料耗材</x:v>
+      </x:c>
+      <x:c r="C69" s="128" t="str">
+        <x:v>低值易耗品</x:v>
+      </x:c>
+      <x:c r="D69" s="131" t="str">
+        <x:v>M10密封舱实心螺栓</x:v>
+      </x:c>
+      <x:c r="E69" s="131" t="str">
+        <x:v>铝制密封螺丝 / M10</x:v>
+      </x:c>
+      <x:c r="F69" s="134" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G69" s="140" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="H69" s="140" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="I69" s="143" t="n">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="J69" s="131" t="str">
+        <x:v>天启ROV97</x:v>
+      </x:c>
+      <x:c r="K69" s="128"/>
+      <x:c r="L69" s="128"/>
+      <x:c r="M69" s="128"/>
+      <x:c r="N69" s="128"/>
+      <x:c r="O69" s="128"/>
+      <x:c r="P69" s="137" t="str">
+        <x:v>2026-08-18</x:v>
+      </x:c>
+      <x:c r="Q69" s="137" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="R69" s="131" t="str">
+        <x:v>包邮；与M10穿线螺丝同单合计370元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="42" customHeight="1">
+      <x:c r="A70" s="129" t="str">
+        <x:v>ZC-20260818-002</x:v>
+      </x:c>
+      <x:c r="B70" s="129" t="str">
+        <x:v>材料耗材</x:v>
+      </x:c>
+      <x:c r="C70" s="129" t="str">
+        <x:v>低值易耗品</x:v>
+      </x:c>
+      <x:c r="D70" s="132" t="str">
+        <x:v>M10穿线螺丝</x:v>
+      </x:c>
+      <x:c r="E70" s="132" t="str">
+        <x:v>银色 / 不锈钢 / M10</x:v>
+      </x:c>
+      <x:c r="F70" s="135" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G70" s="141" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H70" s="141" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="I70" s="144" t="n">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="J70" s="132" t="str">
+        <x:v>天启ROV97</x:v>
+      </x:c>
+      <x:c r="K70" s="129"/>
+      <x:c r="L70" s="129"/>
+      <x:c r="M70" s="129"/>
+      <x:c r="N70" s="129"/>
+      <x:c r="O70" s="129"/>
+      <x:c r="P70" s="138" t="str">
+        <x:v>2026-08-18</x:v>
+      </x:c>
+      <x:c r="Q70" s="138" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="R70" s="132" t="str">
+        <x:v>包邮；与密封舱实心螺栓同单合计370元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="42" customHeight="1">
+      <x:c r="A71" s="128" t="str">
+        <x:v>ZC-20260818-003</x:v>
+      </x:c>
+      <x:c r="B71" s="128" t="str">
+        <x:v>设备及装置</x:v>
+      </x:c>
+      <x:c r="C71" s="128" t="str">
+        <x:v>可周转资产</x:v>
+      </x:c>
+      <x:c r="D71" s="131" t="str">
+        <x:v>TS60水下推进器</x:v>
+      </x:c>
+      <x:c r="E71" s="131" t="str">
+        <x:v>蓝黑500KV正桨 / 推荐12V使用</x:v>
+      </x:c>
+      <x:c r="F71" s="134" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G71" s="140" t="n">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="H71" s="140" t="n">
+        <x:v>567</x:v>
+      </x:c>
+      <x:c r="I71" s="143" t="n">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="J71" s="131" t="str">
+        <x:v>天启ROV97</x:v>
+      </x:c>
+      <x:c r="K71" s="128"/>
+      <x:c r="L71" s="128"/>
+      <x:c r="M71" s="128"/>
+      <x:c r="N71" s="128"/>
+      <x:c r="O71" s="128"/>
+      <x:c r="P71" s="137" t="str">
+        <x:v>2026-08-18</x:v>
+      </x:c>
+      <x:c r="Q71" s="137" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="R71" s="131" t="str">
+        <x:v>包邮；与电调、密封舱同单；优惠后合计1997元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="42" customHeight="1">
+      <x:c r="A72" s="129" t="str">
+        <x:v>ZC-20260818-004</x:v>
+      </x:c>
+      <x:c r="B72" s="129" t="str">
+        <x:v>设备及装置</x:v>
+      </x:c>
+      <x:c r="C72" s="129" t="str">
+        <x:v>可周转资产</x:v>
+      </x:c>
+      <x:c r="D72" s="132" t="str">
+        <x:v>35A双向无刷电调</x:v>
+      </x:c>
+      <x:c r="E72" s="132" t="str">
+        <x:v>35A / 双向 / 水下动力</x:v>
+      </x:c>
+      <x:c r="F72" s="135" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G72" s="141" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="H72" s="141" t="n">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="I72" s="144" t="n">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="J72" s="132" t="str">
+        <x:v>天启ROV97</x:v>
+      </x:c>
+      <x:c r="K72" s="129"/>
+      <x:c r="L72" s="129"/>
+      <x:c r="M72" s="129"/>
+      <x:c r="N72" s="129"/>
+      <x:c r="O72" s="129"/>
+      <x:c r="P72" s="138" t="str">
+        <x:v>2026-08-18</x:v>
+      </x:c>
+      <x:c r="Q72" s="138" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="R72" s="132" t="str">
+        <x:v>包邮；与推进器、密封舱同单；优惠后合计1997元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="72" customHeight="1">
+      <x:c r="A73" s="130" t="str">
+        <x:v>ZC-20260818-005</x:v>
+      </x:c>
+      <x:c r="B73" s="130" t="str">
+        <x:v>设备及装置</x:v>
+      </x:c>
+      <x:c r="C73" s="130" t="str">
+        <x:v>可周转资产</x:v>
+      </x:c>
+      <x:c r="D73" s="133" t="str">
+        <x:v>海目云水下机器人密封舱</x:v>
+      </x:c>
+      <x:c r="E73" s="105" t="str">
+        <x:v>外径160mm×300mm / 亚克力圆管+半球罩+法兰+金属圈+端盖+密封圈+硅脂+配套螺丝</x:v>
+      </x:c>
+      <x:c r="F73" s="136" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G73" s="142" t="n">
+        <x:v>1145</x:v>
+      </x:c>
+      <x:c r="H73" s="142" t="n">
+        <x:v>1145</x:v>
+      </x:c>
+      <x:c r="I73" s="145" t="n">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="J73" s="133" t="str">
+        <x:v>VIOCEAN海目云海洋科技企业店</x:v>
+      </x:c>
+      <x:c r="K73" s="130"/>
+      <x:c r="L73" s="130"/>
+      <x:c r="M73" s="130"/>
+      <x:c r="N73" s="130"/>
+      <x:c r="O73" s="130"/>
+      <x:c r="P73" s="139" t="str">
+        <x:v>2026-08-18</x:v>
+      </x:c>
+      <x:c r="Q73" s="139" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="R73" s="105" t="str">
+        <x:v>优惠后价1145元（标价1150元）；整套含亚克力圆管、半球罩、法兰、金属圈、端盖、密封圈、硅脂和配套螺丝；与推进器、电调同单合计1997元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="42" customHeight="1">
+      <x:c r="A74" s="146" t="str">
+        <x:v>ZC-20260818-006</x:v>
+      </x:c>
+      <x:c r="B74" s="146" t="str">
+        <x:v>电子元器件</x:v>
+      </x:c>
+      <x:c r="C74" s="146" t="str">
+        <x:v>项目组件</x:v>
+      </x:c>
+      <x:c r="D74" s="149" t="str">
+        <x:v>八合一大电流分电板</x:v>
+      </x:c>
+      <x:c r="E74" s="149" t="str">
+        <x:v>输入XT90 / 输出XT60 / 焊好出货</x:v>
+      </x:c>
+      <x:c r="F74" s="152" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G74" s="158" t="n">
+        <x:v>97.5</x:v>
+      </x:c>
+      <x:c r="H74" s="158" t="n">
+        <x:v>97.5</x:v>
+      </x:c>
+      <x:c r="I74" s="161" t="n">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="J74" s="149" t="str">
+        <x:v>梁小二模型</x:v>
+      </x:c>
+      <x:c r="K74" s="146"/>
+      <x:c r="L74" s="146"/>
+      <x:c r="M74" s="146"/>
+      <x:c r="N74" s="146"/>
+      <x:c r="O74" s="146"/>
+      <x:c r="P74" s="155" t="str">
+        <x:v>2026-08-18</x:v>
+      </x:c>
+      <x:c r="Q74" s="155" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="R74" s="149" t="str">
+        <x:v>商品97.50元；运费5.00元另列；实付款102.50元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="42" customHeight="1">
+      <x:c r="A75" s="147" t="str">
+        <x:v>ZC-20260818-007</x:v>
+      </x:c>
+      <x:c r="B75" s="147" t="str">
+        <x:v>电子元器件</x:v>
+      </x:c>
+      <x:c r="C75" s="147" t="str">
+        <x:v>项目组件</x:v>
+      </x:c>
+      <x:c r="D75" s="150" t="str">
+        <x:v>XT90H黑色母头带线</x:v>
+      </x:c>
+      <x:c r="E75" s="150" t="str">
+        <x:v>XT90H黑母头 / 8AWG（8.29mm²）/ 红黑线 / 10cm</x:v>
+      </x:c>
+      <x:c r="F75" s="153" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G75" s="159" t="n">
+        <x:v>10.12</x:v>
+      </x:c>
+      <x:c r="H75" s="159" t="n">
+        <x:v>10.12</x:v>
+      </x:c>
+      <x:c r="I75" s="162" t="n">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="J75" s="150" t="str">
+        <x:v>阳光模型上海DIY（截图店名截断）</x:v>
+      </x:c>
+      <x:c r="K75" s="147"/>
+      <x:c r="L75" s="147"/>
+      <x:c r="M75" s="147"/>
+      <x:c r="N75" s="147"/>
+      <x:c r="O75" s="147"/>
+      <x:c r="P75" s="156" t="str">
+        <x:v>2026-08-18</x:v>
+      </x:c>
+      <x:c r="Q75" s="156" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="R75" s="150" t="str">
+        <x:v>先用后付；确认收货后应付10.12元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" ht="42" customHeight="1">
+      <x:c r="A76" s="148" t="str">
+        <x:v>ZC-20260818-008</x:v>
+      </x:c>
+      <x:c r="B76" s="148" t="str">
+        <x:v>电子元器件</x:v>
+      </x:c>
+      <x:c r="C76" s="148" t="str">
+        <x:v>项目组件</x:v>
+      </x:c>
+      <x:c r="D76" s="151" t="str">
+        <x:v>XT90H黄色公头带线</x:v>
+      </x:c>
+      <x:c r="E76" s="151" t="str">
+        <x:v>XT90H黄公头 / 8AWG（8.29mm²）/ 红黑线 / 10cm</x:v>
+      </x:c>
+      <x:c r="F76" s="154" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G76" s="160" t="n">
+        <x:v>11.11</x:v>
+      </x:c>
+      <x:c r="H76" s="160" t="n">
+        <x:v>11.11</x:v>
+      </x:c>
+      <x:c r="I76" s="163" t="n">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="J76" s="151" t="str">
+        <x:v>阳光模型上海DIY（截图店名截断）</x:v>
+      </x:c>
+      <x:c r="K76" s="148"/>
+      <x:c r="L76" s="148"/>
+      <x:c r="M76" s="148"/>
+      <x:c r="N76" s="148"/>
+      <x:c r="O76" s="148"/>
+      <x:c r="P76" s="157" t="str">
+        <x:v>2026-08-18</x:v>
+      </x:c>
+      <x:c r="Q76" s="157" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="R76" s="151" t="str">
+        <x:v>先用后付；确认收货后应付11.11元</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3403,7 +4248,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d51e598ebdd4b10"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3701e394cbb742cd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3453,16 +4298,16 @@
         <x:v>材料耗材</x:v>
       </x:c>
       <x:c r="B5" s="80" t="n">
-        <x:f>COUNTIF('资产清单'!$B$7:$B$63,A5)</x:f>
-        <x:v>29</x:v>
+        <x:f>COUNTIF('资产清单'!$B$7:$B$76,A5)</x:f>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C5" s="80" t="n">
-        <x:f>SUMIF('资产清单'!$B$7:$B$63,A5,'资产清单'!$F$7:$F$63)</x:f>
-        <x:v>46</x:v>
+        <x:f>SUMIF('资产清单'!$B$7:$B$76,A5,'资产清单'!$F$7:$F$76)</x:f>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D5" s="82" t="n">
-        <x:f>SUMIF('资产清单'!$B$7:$B$63,A5,'资产清单'!$H$7:$H$63)</x:f>
-        <x:v>210.21000000000004</x:v>
+        <x:f>SUMIF('资产清单'!$B$7:$B$76,A5,'资产清单'!$H$7:$H$76)</x:f>
+        <x:v>606.48</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="28" customHeight="1">
@@ -3470,16 +4315,16 @@
         <x:v>电子元器件</x:v>
       </x:c>
       <x:c r="B6" s="80" t="n">
-        <x:f>COUNTIF('资产清单'!$B$7:$B$63,A6)</x:f>
-        <x:v>6</x:v>
+        <x:f>COUNTIF('资产清单'!$B$7:$B$76,A6)</x:f>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C6" s="80" t="n">
-        <x:f>SUMIF('资产清单'!$B$7:$B$63,A6,'资产清单'!$F$7:$F$63)</x:f>
-        <x:v>6</x:v>
+        <x:f>SUMIF('资产清单'!$B$7:$B$76,A6,'资产清单'!$F$7:$F$76)</x:f>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D6" s="82" t="n">
-        <x:f>SUMIF('资产清单'!$B$7:$B$63,A6,'资产清单'!$H$7:$H$63)</x:f>
-        <x:v>166.11999999999998</x:v>
+        <x:f>SUMIF('资产清单'!$B$7:$B$76,A6,'资产清单'!$H$7:$H$76)</x:f>
+        <x:v>300.73</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="28" customHeight="1">
@@ -3487,15 +4332,15 @@
         <x:v>工具器具</x:v>
       </x:c>
       <x:c r="B7" s="80" t="n">
-        <x:f>COUNTIF('资产清单'!$B$7:$B$63,A7)</x:f>
+        <x:f>COUNTIF('资产清单'!$B$7:$B$76,A7)</x:f>
         <x:v>8</x:v>
       </x:c>
       <x:c r="C7" s="80" t="n">
-        <x:f>SUMIF('资产清单'!$B$7:$B$63,A7,'资产清单'!$F$7:$F$63)</x:f>
+        <x:f>SUMIF('资产清单'!$B$7:$B$76,A7,'资产清单'!$F$7:$F$76)</x:f>
         <x:v>8</x:v>
       </x:c>
       <x:c r="D7" s="82" t="n">
-        <x:f>SUMIF('资产清单'!$B$7:$B$63,A7,'资产清单'!$H$7:$H$63)</x:f>
+        <x:f>SUMIF('资产清单'!$B$7:$B$76,A7,'资产清单'!$H$7:$H$76)</x:f>
         <x:v>129.87</x:v>
       </x:c>
     </x:row>
@@ -3504,16 +4349,16 @@
         <x:v>设备及装置</x:v>
       </x:c>
       <x:c r="B8" s="80" t="n">
-        <x:f>COUNTIF('资产清单'!$B$7:$B$63,A8)</x:f>
-        <x:v>11</x:v>
+        <x:f>COUNTIF('资产清单'!$B$7:$B$76,A8)</x:f>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C8" s="80" t="n">
-        <x:f>SUMIF('资产清单'!$B$7:$B$63,A8,'资产清单'!$F$7:$F$63)</x:f>
-        <x:v>11</x:v>
+        <x:f>SUMIF('资产清单'!$B$7:$B$76,A8,'资产清单'!$F$7:$F$76)</x:f>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D8" s="82" t="n">
-        <x:f>SUMIF('资产清单'!$B$7:$B$63,A8,'资产清单'!$H$7:$H$63)</x:f>
-        <x:v>3318.01</x:v>
+        <x:f>SUMIF('资产清单'!$B$7:$B$76,A8,'资产清单'!$H$7:$H$76)</x:f>
+        <x:v>5315.01</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="28" customHeight="1">
@@ -3521,15 +4366,15 @@
         <x:v>仪器仪表</x:v>
       </x:c>
       <x:c r="B9" s="80" t="n">
-        <x:f>COUNTIF('资产清单'!$B$7:$B$63,A9)</x:f>
+        <x:f>COUNTIF('资产清单'!$B$7:$B$76,A9)</x:f>
         <x:v>3</x:v>
       </x:c>
       <x:c r="C9" s="80" t="n">
-        <x:f>SUMIF('资产清单'!$B$7:$B$63,A9,'资产清单'!$F$7:$F$63)</x:f>
+        <x:f>SUMIF('资产清单'!$B$7:$B$76,A9,'资产清单'!$F$7:$F$76)</x:f>
         <x:v>3</x:v>
       </x:c>
       <x:c r="D9" s="82" t="n">
-        <x:f>SUMIF('资产清单'!$B$7:$B$63,A9,'资产清单'!$H$7:$H$63)</x:f>
+        <x:f>SUMIF('资产清单'!$B$7:$B$76,A9,'资产清单'!$H$7:$H$76)</x:f>
         <x:v>320.6</x:v>
       </x:c>
     </x:row>
@@ -3539,15 +4384,15 @@
       </x:c>
       <x:c r="B10" s="81" t="n">
         <x:f>SUM(B5:B9)</x:f>
-        <x:v>57</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C10" s="81" t="n">
         <x:f>SUM(C5:C9)</x:f>
-        <x:v>74</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D10" s="83" t="n">
         <x:f>SUM(D5:D9)</x:f>
-        <x:v>4144.81</x:v>
+        <x:v>6672.6900000000005</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3706,18 +4551,41 @@
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="77" t="str">
+      <x:c r="A9" s="164" t="n">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="B9" s="78" t="str">
+        <x:v>运费</x:v>
+      </x:c>
+      <x:c r="C9" s="89" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D9" s="78" t="str">
+        <x:v>梁小二模型</x:v>
+      </x:c>
+      <x:c r="E9" s="78" t="str">
+        <x:v>2026-08-18</x:v>
+      </x:c>
+      <x:c r="F9" s="78" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G9" s="79" t="str">
+        <x:v>分电板订单：实付款102.50元=商品97.50元+运费5.00元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
         <x:v>费用合计</x:v>
       </x:c>
-      <x:c r="B9" s="78"/>
-      <x:c r="C9" s="89" t="n">
-        <x:f>SUM(C5:C8)</x:f>
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="D9" s="78"/>
-      <x:c r="E9" s="78"/>
-      <x:c r="F9" s="78"/>
-      <x:c r="G9" s="79"/>
+      <x:c r="B10"/>
+      <x:c r="C10" s="90" t="n">
+        <x:f>SUM(C5:C9)</x:f>
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="D10"/>
+      <x:c r="E10"/>
+      <x:c r="F10"/>
+      <x:c r="G10"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="11" t="str">
@@ -3733,7 +4601,7 @@
       </x:c>
       <x:c r="B12" s="90" t="n">
         <x:f>'资产清单'!N3</x:f>
-        <x:v>4144.81</x:v>
+        <x:v>6672.69</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -3741,8 +4609,8 @@
         <x:v>未纳入费用</x:v>
       </x:c>
       <x:c r="B13" s="90" t="n">
-        <x:f>C9</x:f>
-        <x:v>58</x:v>
+        <x:f>C10</x:f>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -3751,7 +4619,7 @@
       </x:c>
       <x:c r="B14" s="90" t="n">
         <x:f>B12+B13</x:f>
-        <x:v>4202.81</x:v>
+        <x:v>6735.69</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -3759,7 +4627,7 @@
         <x:v>原采购总额</x:v>
       </x:c>
       <x:c r="B15" s="90" t="n">
-        <x:v>4202.81</x:v>
+        <x:v>6735.69</x:v>
       </x:c>
     </x:row>
     <x:row r="16">

--- a/物资/资产清单.xlsx
+++ b/物资/资产清单.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产清单" sheetId="1" r:id="R278bb2551c7748e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类汇总" sheetId="2" r:id="R459c318a253b45ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="未纳入资产" sheetId="3" r:id="R336099e4b0e94b20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产清单" sheetId="1" r:id="R78d6d692dae8419c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类汇总" sheetId="2" r:id="R59bfbd9da86d4fe2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="未纳入资产" sheetId="3" r:id="R186f70744ee748c2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -96,7 +96,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="15">
+  <x:fills count="17">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -166,6 +166,16 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -240,7 +250,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="165">
+  <x:cellXfs count="183">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -630,6 +640,60 @@
       <x:alignment horizontal="center" vertical="center" wrapText="0"/>
     </x:xf>
     <x:xf numFmtId="202" fontId="3" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="16" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="16" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="16" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="16" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="12" fillId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="12" fillId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="12" fillId="16" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="12" fillId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="12" fillId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="12" fillId="16" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -638,8 +702,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AssetsTable" displayName="AssetsTable" ref="A6:R76" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A6:R76"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AssetsTable" displayName="AssetsTable" ref="A6:R86" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A6:R86"/>
   <x:tableColumns count="18">
     <x:tableColumn id="1" name="资产编号"/>
     <x:tableColumn id="2" name="管理类别"/>
@@ -930,8 +994,8 @@
       <x:c r="B3" s="19"/>
       <x:c r="C3" s="20"/>
       <x:c r="D3" s="27" t="n">
-        <x:f>COUNTA(A7:A76)</x:f>
-        <x:v>70</x:v>
+        <x:f>COUNTA(A7:A86)</x:f>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E3" s="28"/>
       <x:c r="F3" s="18" t="str">
@@ -940,8 +1004,8 @@
       <x:c r="G3" s="19"/>
       <x:c r="H3" s="20"/>
       <x:c r="I3" s="27" t="n">
-        <x:f>SUM(F7:F76)</x:f>
-        <x:v>102</x:v>
+        <x:f>SUM(F7:F86)</x:f>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="J3" s="28"/>
       <x:c r="K3" s="18" t="str">
@@ -950,8 +1014,8 @@
       <x:c r="L3" s="19"/>
       <x:c r="M3" s="20"/>
       <x:c r="N3" s="32" t="n">
-        <x:f>SUM(H7:H76)</x:f>
-        <x:v>6672.69</x:v>
+        <x:f>SUM(H7:H86)</x:f>
+        <x:v>8526.73</x:v>
       </x:c>
       <x:c r="O3" s="33"/>
       <x:c r="P3" s="33"/>
@@ -4222,6 +4286,466 @@
       </x:c>
       <x:c r="R76" s="151" t="str">
         <x:v>先用后付；确认收货后应付11.11元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" ht="48" customHeight="1">
+      <x:c r="A77" s="165" t="str">
+        <x:v>ZC-20260825-001</x:v>
+      </x:c>
+      <x:c r="B77" s="165" t="str">
+        <x:v>工具器具</x:v>
+      </x:c>
+      <x:c r="C77" s="165" t="str">
+        <x:v>通用工具</x:v>
+      </x:c>
+      <x:c r="D77" s="168" t="str">
+        <x:v>密封舱气密性测试套装</x:v>
+      </x:c>
+      <x:c r="E77" s="168" t="str">
+        <x:v>真空枪+宝塔气嘴 / 工具箱套装</x:v>
+      </x:c>
+      <x:c r="F77" s="171" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G77" s="177" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="H77" s="177" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="I77" s="180" t="n">
+        <x:v>46259</x:v>
+      </x:c>
+      <x:c r="J77" s="168" t="str">
+        <x:v>VIOCEAN海目云海洋科技企业店</x:v>
+      </x:c>
+      <x:c r="K77" s="165"/>
+      <x:c r="L77" s="165"/>
+      <x:c r="M77" s="165"/>
+      <x:c r="N77" s="165"/>
+      <x:c r="O77" s="165"/>
+      <x:c r="P77" s="174" t="str">
+        <x:v>2026-08-25</x:v>
+      </x:c>
+      <x:c r="Q77" s="174" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="R77" s="168" t="str">
+        <x:v>实付款245元；图1、2为同一订单，去重登记</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" ht="48" customHeight="1">
+      <x:c r="A78" s="166" t="str">
+        <x:v>ZC-20260825-002</x:v>
+      </x:c>
+      <x:c r="B78" s="166" t="str">
+        <x:v>材料耗材</x:v>
+      </x:c>
+      <x:c r="C78" s="166" t="str">
+        <x:v>低值易耗品</x:v>
+      </x:c>
+      <x:c r="D78" s="169" t="str">
+        <x:v>黑色快干AB环氧树脂胶</x:v>
+      </x:c>
+      <x:c r="E78" s="169" t="str">
+        <x:v>黑色快干款 / 5分钟初固 / 两支装 / 送工具</x:v>
+      </x:c>
+      <x:c r="F78" s="172" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G78" s="178" t="n">
+        <x:v>15.1</x:v>
+      </x:c>
+      <x:c r="H78" s="178" t="n">
+        <x:v>15.1</x:v>
+      </x:c>
+      <x:c r="I78" s="181" t="n">
+        <x:v>46259</x:v>
+      </x:c>
+      <x:c r="J78" s="169" t="str">
+        <x:v>固万旗舰店</x:v>
+      </x:c>
+      <x:c r="K78" s="166"/>
+      <x:c r="L78" s="166"/>
+      <x:c r="M78" s="166"/>
+      <x:c r="N78" s="166"/>
+      <x:c r="O78" s="166"/>
+      <x:c r="P78" s="175" t="str">
+        <x:v>2026-08-25</x:v>
+      </x:c>
+      <x:c r="Q78" s="175" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="R78" s="169" t="str">
+        <x:v>先用后付；确认收货后应付15.10元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" ht="48" customHeight="1">
+      <x:c r="A79" s="165" t="str">
+        <x:v>ZC-20260825-003</x:v>
+      </x:c>
+      <x:c r="B79" s="165" t="str">
+        <x:v>设备及装置</x:v>
+      </x:c>
+      <x:c r="C79" s="165" t="str">
+        <x:v>项目组件</x:v>
+      </x:c>
+      <x:c r="D79" s="168" t="str">
+        <x:v>4S6P水下机器人锂电池</x:v>
+      </x:c>
+      <x:c r="E79" s="168" t="str">
+        <x:v>14.8V / 18Ah / 4S6P</x:v>
+      </x:c>
+      <x:c r="F79" s="171" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G79" s="177" t="n">
+        <x:v>1552</x:v>
+      </x:c>
+      <x:c r="H79" s="177" t="n">
+        <x:v>1552</x:v>
+      </x:c>
+      <x:c r="I79" s="180" t="n">
+        <x:v>46259</x:v>
+      </x:c>
+      <x:c r="J79" s="168" t="str">
+        <x:v>仙藤电池</x:v>
+      </x:c>
+      <x:c r="K79" s="165"/>
+      <x:c r="L79" s="165"/>
+      <x:c r="M79" s="165"/>
+      <x:c r="N79" s="165"/>
+      <x:c r="O79" s="165"/>
+      <x:c r="P79" s="174" t="str">
+        <x:v>2026-08-25</x:v>
+      </x:c>
+      <x:c r="Q79" s="174" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="R79" s="168" t="str">
+        <x:v>实付款1552.00元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" ht="48" customHeight="1">
+      <x:c r="A80" s="166" t="str">
+        <x:v>ZC-20260826-001</x:v>
+      </x:c>
+      <x:c r="B80" s="166" t="str">
+        <x:v>材料耗材</x:v>
+      </x:c>
+      <x:c r="C80" s="166" t="str">
+        <x:v>低值易耗品</x:v>
+      </x:c>
+      <x:c r="D80" s="169" t="str">
+        <x:v>M2.5 304不锈钢六角螺母</x:v>
+      </x:c>
+      <x:c r="E80" s="169" t="str">
+        <x:v>M2.5 / 100个</x:v>
+      </x:c>
+      <x:c r="F80" s="172" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G80" s="178" t="n">
+        <x:v>2.46</x:v>
+      </x:c>
+      <x:c r="H80" s="178" t="n">
+        <x:v>2.46</x:v>
+      </x:c>
+      <x:c r="I80" s="181" t="n">
+        <x:v>46260</x:v>
+      </x:c>
+      <x:c r="J80" s="169" t="str">
+        <x:v>金超官方旗舰店</x:v>
+      </x:c>
+      <x:c r="K80" s="166"/>
+      <x:c r="L80" s="166"/>
+      <x:c r="M80" s="166"/>
+      <x:c r="N80" s="166"/>
+      <x:c r="O80" s="166"/>
+      <x:c r="P80" s="175" t="str">
+        <x:v>2026-08-26</x:v>
+      </x:c>
+      <x:c r="Q80" s="175" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="R80" s="169" t="str">
+        <x:v>先用后付；确认收货后应付2.46元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="48" customHeight="1">
+      <x:c r="A81" s="165" t="str">
+        <x:v>ZC-20260826-002</x:v>
+      </x:c>
+      <x:c r="B81" s="165" t="str">
+        <x:v>材料耗材</x:v>
+      </x:c>
+      <x:c r="C81" s="165" t="str">
+        <x:v>低值易耗品</x:v>
+      </x:c>
+      <x:c r="D81" s="168" t="str">
+        <x:v>M2.5尼龙平垫片</x:v>
+      </x:c>
+      <x:c r="E81" s="168" t="str">
+        <x:v>M2.5×5×1mm / 200个</x:v>
+      </x:c>
+      <x:c r="F81" s="171" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G81" s="177" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H81" s="177" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I81" s="180" t="n">
+        <x:v>46260</x:v>
+      </x:c>
+      <x:c r="J81" s="168" t="str">
+        <x:v>品诺塑胶垫圈供应商</x:v>
+      </x:c>
+      <x:c r="K81" s="165"/>
+      <x:c r="L81" s="165"/>
+      <x:c r="M81" s="165"/>
+      <x:c r="N81" s="165"/>
+      <x:c r="O81" s="165"/>
+      <x:c r="P81" s="174" t="str">
+        <x:v>2026-08-26</x:v>
+      </x:c>
+      <x:c r="Q81" s="174" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="R81" s="168" t="str">
+        <x:v>先用后付；确认收货后应付4.00元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" ht="48" customHeight="1">
+      <x:c r="A82" s="166" t="str">
+        <x:v>ZC-20260826-003</x:v>
+      </x:c>
+      <x:c r="B82" s="166" t="str">
+        <x:v>材料耗材</x:v>
+      </x:c>
+      <x:c r="C82" s="166" t="str">
+        <x:v>低值易耗品</x:v>
+      </x:c>
+      <x:c r="D82" s="169" t="str">
+        <x:v>M2.5×8 304不锈钢十字圆头机牙螺钉</x:v>
+      </x:c>
+      <x:c r="E82" s="169" t="str">
+        <x:v>M2.5×8 / 200个</x:v>
+      </x:c>
+      <x:c r="F82" s="172" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G82" s="178" t="n">
+        <x:v>5.71</x:v>
+      </x:c>
+      <x:c r="H82" s="178" t="n">
+        <x:v>5.71</x:v>
+      </x:c>
+      <x:c r="I82" s="181" t="n">
+        <x:v>46260</x:v>
+      </x:c>
+      <x:c r="J82" s="169" t="str">
+        <x:v>伯瑞特官方旗舰店</x:v>
+      </x:c>
+      <x:c r="K82" s="166"/>
+      <x:c r="L82" s="166"/>
+      <x:c r="M82" s="166"/>
+      <x:c r="N82" s="166"/>
+      <x:c r="O82" s="166"/>
+      <x:c r="P82" s="175" t="str">
+        <x:v>2026-08-26</x:v>
+      </x:c>
+      <x:c r="Q82" s="175" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="R82" s="169" t="str">
+        <x:v>先用后付；确认收货后应付5.71元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="48" customHeight="1">
+      <x:c r="A83" s="165" t="str">
+        <x:v>ZC-20260826-004</x:v>
+      </x:c>
+      <x:c r="B83" s="165" t="str">
+        <x:v>材料耗材</x:v>
+      </x:c>
+      <x:c r="C83" s="165" t="str">
+        <x:v>低值易耗品</x:v>
+      </x:c>
+      <x:c r="D83" s="168" t="str">
+        <x:v>M2.5×6 304不锈钢十字圆头机牙螺钉</x:v>
+      </x:c>
+      <x:c r="E83" s="168" t="str">
+        <x:v>M2.5×6 / 200个</x:v>
+      </x:c>
+      <x:c r="F83" s="171" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G83" s="177" t="n">
+        <x:v>5.07</x:v>
+      </x:c>
+      <x:c r="H83" s="177" t="n">
+        <x:v>5.07</x:v>
+      </x:c>
+      <x:c r="I83" s="180" t="n">
+        <x:v>46260</x:v>
+      </x:c>
+      <x:c r="J83" s="168" t="str">
+        <x:v>伯瑞特官方旗舰店</x:v>
+      </x:c>
+      <x:c r="K83" s="165"/>
+      <x:c r="L83" s="165"/>
+      <x:c r="M83" s="165"/>
+      <x:c r="N83" s="165"/>
+      <x:c r="O83" s="165"/>
+      <x:c r="P83" s="174" t="str">
+        <x:v>2026-08-26</x:v>
+      </x:c>
+      <x:c r="Q83" s="174" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="R83" s="168" t="str">
+        <x:v>先用后付；确认收货后应付5.07元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" ht="48" customHeight="1">
+      <x:c r="A84" s="166" t="str">
+        <x:v>ZC-20260826-005</x:v>
+      </x:c>
+      <x:c r="B84" s="166" t="str">
+        <x:v>材料耗材</x:v>
+      </x:c>
+      <x:c r="C84" s="166" t="str">
+        <x:v>低值易耗品</x:v>
+      </x:c>
+      <x:c r="D84" s="169" t="str">
+        <x:v>M2.5×10 304不锈钢十字圆头机牙螺钉</x:v>
+      </x:c>
+      <x:c r="E84" s="169" t="str">
+        <x:v>M2.5×10 / 200个</x:v>
+      </x:c>
+      <x:c r="F84" s="172" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G84" s="178" t="n">
+        <x:v>6.19</x:v>
+      </x:c>
+      <x:c r="H84" s="178" t="n">
+        <x:v>6.19</x:v>
+      </x:c>
+      <x:c r="I84" s="181" t="n">
+        <x:v>46260</x:v>
+      </x:c>
+      <x:c r="J84" s="169" t="str">
+        <x:v>伯瑞特官方旗舰店</x:v>
+      </x:c>
+      <x:c r="K84" s="166"/>
+      <x:c r="L84" s="166"/>
+      <x:c r="M84" s="166"/>
+      <x:c r="N84" s="166"/>
+      <x:c r="O84" s="166"/>
+      <x:c r="P84" s="175" t="str">
+        <x:v>2026-08-26</x:v>
+      </x:c>
+      <x:c r="Q84" s="175" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="R84" s="169" t="str">
+        <x:v>先用后付；确认收货后应付6.19元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" ht="48" customHeight="1">
+      <x:c r="A85" s="165" t="str">
+        <x:v>ZC-20260826-006</x:v>
+      </x:c>
+      <x:c r="B85" s="165" t="str">
+        <x:v>材料耗材</x:v>
+      </x:c>
+      <x:c r="C85" s="165" t="str">
+        <x:v>低值易耗品</x:v>
+      </x:c>
+      <x:c r="D85" s="168" t="str">
+        <x:v>黑色自锁式尼龙扎带</x:v>
+      </x:c>
+      <x:c r="E85" s="168" t="str">
+        <x:v>4×150mm / 黑色 / 500根</x:v>
+      </x:c>
+      <x:c r="F85" s="171" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G85" s="177" t="n">
+        <x:v>17.39</x:v>
+      </x:c>
+      <x:c r="H85" s="177" t="n">
+        <x:v>17.39</x:v>
+      </x:c>
+      <x:c r="I85" s="180" t="n">
+        <x:v>46260</x:v>
+      </x:c>
+      <x:c r="J85" s="168" t="str">
+        <x:v>伯瑞特官方旗舰店</x:v>
+      </x:c>
+      <x:c r="K85" s="165"/>
+      <x:c r="L85" s="165"/>
+      <x:c r="M85" s="165"/>
+      <x:c r="N85" s="165"/>
+      <x:c r="O85" s="165"/>
+      <x:c r="P85" s="174" t="str">
+        <x:v>2026-08-26</x:v>
+      </x:c>
+      <x:c r="Q85" s="174" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="R85" s="168" t="str">
+        <x:v>先用后付；确认收货后应付17.39元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" ht="48" customHeight="1">
+      <x:c r="A86" s="167" t="str">
+        <x:v>ZC-20260826-007</x:v>
+      </x:c>
+      <x:c r="B86" s="167" t="str">
+        <x:v>材料耗材</x:v>
+      </x:c>
+      <x:c r="C86" s="167" t="str">
+        <x:v>低值易耗品</x:v>
+      </x:c>
+      <x:c r="D86" s="170" t="str">
+        <x:v>M3×20 304不锈钢杯头内六角螺钉</x:v>
+      </x:c>
+      <x:c r="E86" s="170" t="str">
+        <x:v>M3×20 / 50个</x:v>
+      </x:c>
+      <x:c r="F86" s="173" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G86" s="179" t="n">
+        <x:v>1.12</x:v>
+      </x:c>
+      <x:c r="H86" s="179" t="n">
+        <x:v>1.12</x:v>
+      </x:c>
+      <x:c r="I86" s="182" t="n">
+        <x:v>46260</x:v>
+      </x:c>
+      <x:c r="J86" s="170" t="str">
+        <x:v>资鑫旗舰店</x:v>
+      </x:c>
+      <x:c r="K86" s="167"/>
+      <x:c r="L86" s="167"/>
+      <x:c r="M86" s="167"/>
+      <x:c r="N86" s="167"/>
+      <x:c r="O86" s="167"/>
+      <x:c r="P86" s="176" t="str">
+        <x:v>2026-08-26</x:v>
+      </x:c>
+      <x:c r="Q86" s="176" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="R86" s="170" t="str">
+        <x:v>先用后付；确认收货后应付1.12元</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4248,7 +4772,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3701e394cbb742cd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R40c134a449a5490b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4298,16 +4822,16 @@
         <x:v>材料耗材</x:v>
       </x:c>
       <x:c r="B5" s="80" t="n">
-        <x:f>COUNTIF('资产清单'!$B$7:$B$76,A5)</x:f>
-        <x:v>35</x:v>
+        <x:f>COUNTIF('资产清单'!$B$7:$B$86,A5)</x:f>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C5" s="80" t="n">
-        <x:f>SUMIF('资产清单'!$B$7:$B$76,A5,'资产清单'!$F$7:$F$76)</x:f>
-        <x:v>63</x:v>
+        <x:f>SUMIF('资产清单'!$B$7:$B$86,A5,'资产清单'!$F$7:$F$86)</x:f>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D5" s="82" t="n">
-        <x:f>SUMIF('资产清单'!$B$7:$B$76,A5,'资产清单'!$H$7:$H$76)</x:f>
-        <x:v>606.48</x:v>
+        <x:f>SUMIF('资产清单'!$B$7:$B$86,A5,'资产清单'!$H$7:$H$86)</x:f>
+        <x:v>663.5200000000002</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="28" customHeight="1">
@@ -4315,15 +4839,15 @@
         <x:v>电子元器件</x:v>
       </x:c>
       <x:c r="B6" s="80" t="n">
-        <x:f>COUNTIF('资产清单'!$B$7:$B$76,A6)</x:f>
+        <x:f>COUNTIF('资产清单'!$B$7:$B$86,A6)</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="C6" s="80" t="n">
-        <x:f>SUMIF('资产清单'!$B$7:$B$76,A6,'资产清单'!$F$7:$F$76)</x:f>
+        <x:f>SUMIF('资产清单'!$B$7:$B$86,A6,'资产清单'!$F$7:$F$86)</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="D6" s="82" t="n">
-        <x:f>SUMIF('资产清单'!$B$7:$B$76,A6,'资产清单'!$H$7:$H$76)</x:f>
+        <x:f>SUMIF('资产清单'!$B$7:$B$86,A6,'资产清单'!$H$7:$H$86)</x:f>
         <x:v>300.73</x:v>
       </x:c>
     </x:row>
@@ -4332,16 +4856,16 @@
         <x:v>工具器具</x:v>
       </x:c>
       <x:c r="B7" s="80" t="n">
-        <x:f>COUNTIF('资产清单'!$B$7:$B$76,A7)</x:f>
-        <x:v>8</x:v>
+        <x:f>COUNTIF('资产清单'!$B$7:$B$86,A7)</x:f>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C7" s="80" t="n">
-        <x:f>SUMIF('资产清单'!$B$7:$B$76,A7,'资产清单'!$F$7:$F$76)</x:f>
-        <x:v>8</x:v>
+        <x:f>SUMIF('资产清单'!$B$7:$B$86,A7,'资产清单'!$F$7:$F$86)</x:f>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D7" s="82" t="n">
-        <x:f>SUMIF('资产清单'!$B$7:$B$76,A7,'资产清单'!$H$7:$H$76)</x:f>
-        <x:v>129.87</x:v>
+        <x:f>SUMIF('资产清单'!$B$7:$B$86,A7,'资产清单'!$H$7:$H$86)</x:f>
+        <x:v>374.87</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="28" customHeight="1">
@@ -4349,16 +4873,16 @@
         <x:v>设备及装置</x:v>
       </x:c>
       <x:c r="B8" s="80" t="n">
-        <x:f>COUNTIF('资产清单'!$B$7:$B$76,A8)</x:f>
-        <x:v>14</x:v>
+        <x:f>COUNTIF('资产清单'!$B$7:$B$86,A8)</x:f>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C8" s="80" t="n">
-        <x:f>SUMIF('资产清单'!$B$7:$B$76,A8,'资产清单'!$F$7:$F$76)</x:f>
-        <x:v>18</x:v>
+        <x:f>SUMIF('资产清单'!$B$7:$B$86,A8,'资产清单'!$F$7:$F$86)</x:f>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D8" s="82" t="n">
-        <x:f>SUMIF('资产清单'!$B$7:$B$76,A8,'资产清单'!$H$7:$H$76)</x:f>
-        <x:v>5315.01</x:v>
+        <x:f>SUMIF('资产清单'!$B$7:$B$86,A8,'资产清单'!$H$7:$H$86)</x:f>
+        <x:v>6867.01</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="28" customHeight="1">
@@ -4366,15 +4890,15 @@
         <x:v>仪器仪表</x:v>
       </x:c>
       <x:c r="B9" s="80" t="n">
-        <x:f>COUNTIF('资产清单'!$B$7:$B$76,A9)</x:f>
+        <x:f>COUNTIF('资产清单'!$B$7:$B$86,A9)</x:f>
         <x:v>3</x:v>
       </x:c>
       <x:c r="C9" s="80" t="n">
-        <x:f>SUMIF('资产清单'!$B$7:$B$76,A9,'资产清单'!$F$7:$F$76)</x:f>
+        <x:f>SUMIF('资产清单'!$B$7:$B$86,A9,'资产清单'!$F$7:$F$86)</x:f>
         <x:v>3</x:v>
       </x:c>
       <x:c r="D9" s="82" t="n">
-        <x:f>SUMIF('资产清单'!$B$7:$B$76,A9,'资产清单'!$H$7:$H$76)</x:f>
+        <x:f>SUMIF('资产清单'!$B$7:$B$86,A9,'资产清单'!$H$7:$H$86)</x:f>
         <x:v>320.6</x:v>
       </x:c>
     </x:row>
@@ -4384,15 +4908,15 @@
       </x:c>
       <x:c r="B10" s="81" t="n">
         <x:f>SUM(B5:B9)</x:f>
-        <x:v>70</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C10" s="81" t="n">
         <x:f>SUM(C5:C9)</x:f>
-        <x:v>102</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D10" s="83" t="n">
         <x:f>SUM(D5:D9)</x:f>
-        <x:v>6672.6900000000005</x:v>
+        <x:v>8526.730000000001</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4601,7 +5125,7 @@
       </x:c>
       <x:c r="B12" s="90" t="n">
         <x:f>'资产清单'!N3</x:f>
-        <x:v>6672.69</x:v>
+        <x:v>8526.73</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -4619,7 +5143,7 @@
       </x:c>
       <x:c r="B14" s="90" t="n">
         <x:f>B12+B13</x:f>
-        <x:v>6735.69</x:v>
+        <x:v>8589.73</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -4627,7 +5151,7 @@
         <x:v>原采购总额</x:v>
       </x:c>
       <x:c r="B15" s="90" t="n">
-        <x:v>6735.69</x:v>
+        <x:v>8589.73</x:v>
       </x:c>
     </x:row>
     <x:row r="16">

--- a/物资/资产清单.xlsx
+++ b/物资/资产清单.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产清单" sheetId="1" r:id="R78d6d692dae8419c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类汇总" sheetId="2" r:id="R59bfbd9da86d4fe2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="未纳入资产" sheetId="3" r:id="R186f70744ee748c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产清单" sheetId="1" r:id="R4768592e950644a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类汇总" sheetId="2" r:id="R57a8495103d24375"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="未纳入资产" sheetId="3" r:id="R91bbb4e5f852463f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -21,7 +21,7 @@
     <x:numFmt numFmtId="202" formatCode="yyyy-mm-dd"/>
     <x:numFmt numFmtId="203" formatCode="0"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="15">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -95,8 +95,18 @@
       <x:color rgb="FF203040"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF203040"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF203040"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="17">
+  <x:fills count="19">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -166,6 +176,16 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -250,7 +270,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="183">
+  <x:cellXfs count="234">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -694,6 +714,121 @@
     <x:xf numFmtId="202" fontId="12" fillId="16" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="17" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="17" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="17" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="17" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="12" fillId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="12" fillId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="12" fillId="17" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="12" fillId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="12" fillId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="12" fillId="17" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="3" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="13" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="13" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="14" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="13" fillId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0"/>
+    <x:xf numFmtId="0" fontId="13" fillId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0"/>
+    <x:xf numFmtId="200" fontId="13" fillId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0"/>
+    <x:xf numFmtId="202" fontId="14" fillId="18" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="18" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="13" fillId="18" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="18" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="13" fillId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="13" fillId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="14" fillId="18" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="18" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="13" fillId="18" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="18" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="13" fillId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="14" fillId="18" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="18" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="13" fillId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="13" fillId="18" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="18" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -702,8 +837,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AssetsTable" displayName="AssetsTable" ref="A6:R86" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A6:R86"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AssetsTable" displayName="AssetsTable" ref="A6:R93" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A6:R93"/>
   <x:tableColumns count="18">
     <x:tableColumn id="1" name="资产编号"/>
     <x:tableColumn id="2" name="管理类别"/>
@@ -994,8 +1129,8 @@
       <x:c r="B3" s="19"/>
       <x:c r="C3" s="20"/>
       <x:c r="D3" s="27" t="n">
-        <x:f>COUNTA(A7:A86)</x:f>
-        <x:v>80</x:v>
+        <x:f>COUNTA(A7:A93)</x:f>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E3" s="28"/>
       <x:c r="F3" s="18" t="str">
@@ -1004,8 +1139,8 @@
       <x:c r="G3" s="19"/>
       <x:c r="H3" s="20"/>
       <x:c r="I3" s="27" t="n">
-        <x:f>SUM(F7:F86)</x:f>
-        <x:v>112</x:v>
+        <x:f>SUM(F7:F93)</x:f>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="J3" s="28"/>
       <x:c r="K3" s="18" t="str">
@@ -1014,8 +1149,8 @@
       <x:c r="L3" s="19"/>
       <x:c r="M3" s="20"/>
       <x:c r="N3" s="32" t="n">
-        <x:f>SUM(H7:H86)</x:f>
-        <x:v>8526.73</x:v>
+        <x:f>SUM(H7:H93)</x:f>
+        <x:v>9146.69</x:v>
       </x:c>
       <x:c r="O3" s="33"/>
       <x:c r="P3" s="33"/>
@@ -4746,6 +4881,328 @@
       </x:c>
       <x:c r="R86" s="170" t="str">
         <x:v>先用后付；确认收货后应付1.12元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" ht="48" customHeight="1">
+      <x:c r="A87" s="183" t="str">
+        <x:v>ZC-20260828-001</x:v>
+      </x:c>
+      <x:c r="B87" s="183" t="str">
+        <x:v>材料耗材</x:v>
+      </x:c>
+      <x:c r="C87" s="183" t="str">
+        <x:v>低值易耗品</x:v>
+      </x:c>
+      <x:c r="D87" s="186" t="str">
+        <x:v>ROV专用防水密封硅脂</x:v>
+      </x:c>
+      <x:c r="E87" s="186" t="str">
+        <x:v>水下密封专用硅脂</x:v>
+      </x:c>
+      <x:c r="F87" s="189" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G87" s="195" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="H87" s="195" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="I87" s="198" t="n">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="J87" s="186" t="str">
+        <x:v>VIOCEAN海目云海洋科技企业店</x:v>
+      </x:c>
+      <x:c r="K87" s="183"/>
+      <x:c r="L87" s="183"/>
+      <x:c r="M87" s="183"/>
+      <x:c r="N87" s="183"/>
+      <x:c r="O87" s="183"/>
+      <x:c r="P87" s="192" t="str">
+        <x:v>2026-08-28</x:v>
+      </x:c>
+      <x:c r="Q87" s="192" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="R87" s="186" t="str">
+        <x:v>已签收；商品金额49.00元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" ht="48" customHeight="1">
+      <x:c r="A88" s="184" t="str">
+        <x:v>ZC-20260828-002</x:v>
+      </x:c>
+      <x:c r="B88" s="184" t="str">
+        <x:v>材料耗材</x:v>
+      </x:c>
+      <x:c r="C88" s="184" t="str">
+        <x:v>低值易耗品</x:v>
+      </x:c>
+      <x:c r="D88" s="187" t="str">
+        <x:v>水下机器人穿线密封胶</x:v>
+      </x:c>
+      <x:c r="E88" s="187" t="str">
+        <x:v>400米耐压密封胶 / 赠推杆和5个胶管</x:v>
+      </x:c>
+      <x:c r="F88" s="190" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G88" s="196" t="n">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="H88" s="196" t="n">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="I88" s="199" t="n">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="J88" s="187" t="str">
+        <x:v>VIOCEAN海目云海洋科技企业店</x:v>
+      </x:c>
+      <x:c r="K88" s="184"/>
+      <x:c r="L88" s="184"/>
+      <x:c r="M88" s="184"/>
+      <x:c r="N88" s="184"/>
+      <x:c r="O88" s="184"/>
+      <x:c r="P88" s="193" t="str">
+        <x:v>2026-08-28</x:v>
+      </x:c>
+      <x:c r="Q88" s="193" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="R88" s="187" t="str">
+        <x:v>已签收；商品金额75.00元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" ht="48" customHeight="1">
+      <x:c r="A89" s="183" t="str">
+        <x:v>ZC-20260828-003</x:v>
+      </x:c>
+      <x:c r="B89" s="183" t="str">
+        <x:v>设备及装置</x:v>
+      </x:c>
+      <x:c r="C89" s="183" t="str">
+        <x:v>项目组件</x:v>
+      </x:c>
+      <x:c r="D89" s="186" t="str">
+        <x:v>ROV纯铅配重块</x:v>
+      </x:c>
+      <x:c r="E89" s="186" t="str">
+        <x:v>约200g/块</x:v>
+      </x:c>
+      <x:c r="F89" s="189" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G89" s="195" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="H89" s="195" t="n">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="I89" s="198" t="n">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="J89" s="186" t="str">
+        <x:v>VIOCEAN海目云海洋科技企业店</x:v>
+      </x:c>
+      <x:c r="K89" s="183"/>
+      <x:c r="L89" s="183"/>
+      <x:c r="M89" s="183"/>
+      <x:c r="N89" s="183"/>
+      <x:c r="O89" s="183"/>
+      <x:c r="P89" s="192" t="str">
+        <x:v>2026-08-28</x:v>
+      </x:c>
+      <x:c r="Q89" s="192" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="R89" s="186" t="str">
+        <x:v>已签收；5块共115.00元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" ht="48" customHeight="1">
+      <x:c r="A90" s="184" t="str">
+        <x:v>ZC-20260828-004</x:v>
+      </x:c>
+      <x:c r="B90" s="184" t="str">
+        <x:v>工具器具</x:v>
+      </x:c>
+      <x:c r="C90" s="184" t="str">
+        <x:v>通用工具</x:v>
+      </x:c>
+      <x:c r="D90" s="187" t="str">
+        <x:v>1:1 AB胶枪</x:v>
+      </x:c>
+      <x:c r="E90" s="187" t="str">
+        <x:v>AB胶枪 / 1比1</x:v>
+      </x:c>
+      <x:c r="F90" s="190" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G90" s="196" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="H90" s="196" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="I90" s="199" t="n">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="J90" s="187" t="str">
+        <x:v>VIOCEAN海目云海洋科技企业店</x:v>
+      </x:c>
+      <x:c r="K90" s="184"/>
+      <x:c r="L90" s="184"/>
+      <x:c r="M90" s="184"/>
+      <x:c r="N90" s="184"/>
+      <x:c r="O90" s="184"/>
+      <x:c r="P90" s="193" t="str">
+        <x:v>2026-08-28</x:v>
+      </x:c>
+      <x:c r="Q90" s="193" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="R90" s="187" t="str">
+        <x:v>已签收；商品金额45.00元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" ht="48" customHeight="1">
+      <x:c r="A91" s="183" t="str">
+        <x:v>ZC-20260828-005</x:v>
+      </x:c>
+      <x:c r="B91" s="183" t="str">
+        <x:v>设备及装置</x:v>
+      </x:c>
+      <x:c r="C91" s="183" t="str">
+        <x:v>可周转资产</x:v>
+      </x:c>
+      <x:c r="D91" s="186" t="str">
+        <x:v>水下机器人ROV探照灯</x:v>
+      </x:c>
+      <x:c r="E91" s="186" t="str">
+        <x:v>6500K / ArduSub脉宽控制 / 100°光束角</x:v>
+      </x:c>
+      <x:c r="F91" s="189" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G91" s="195" t="n">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="H91" s="195" t="n">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="I91" s="198" t="n">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="J91" s="186" t="str">
+        <x:v>EXOCEAN拓洲智能</x:v>
+      </x:c>
+      <x:c r="K91" s="183"/>
+      <x:c r="L91" s="183"/>
+      <x:c r="M91" s="183"/>
+      <x:c r="N91" s="183"/>
+      <x:c r="O91" s="183"/>
+      <x:c r="P91" s="192" t="str">
+        <x:v>2026-08-28</x:v>
+      </x:c>
+      <x:c r="Q91" s="192" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="R91" s="186" t="str">
+        <x:v>商品标价299.00元；实付311.00元，差额12.00元另列</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" ht="48" customHeight="1">
+      <x:c r="A92" s="184" t="str">
+        <x:v>ZC-20260828-006</x:v>
+      </x:c>
+      <x:c r="B92" s="184" t="str">
+        <x:v>材料耗材</x:v>
+      </x:c>
+      <x:c r="C92" s="184" t="str">
+        <x:v>低值易耗品</x:v>
+      </x:c>
+      <x:c r="D92" s="187" t="str">
+        <x:v>M5×16 304不锈钢杯头内六角螺钉</x:v>
+      </x:c>
+      <x:c r="E92" s="187" t="str">
+        <x:v>M5×16 / 50个</x:v>
+      </x:c>
+      <x:c r="F92" s="190" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G92" s="196" t="n">
+        <x:v>5.36</x:v>
+      </x:c>
+      <x:c r="H92" s="196" t="n">
+        <x:v>5.36</x:v>
+      </x:c>
+      <x:c r="I92" s="199" t="n">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="J92" s="187" t="str">
+        <x:v>伯瑞特官方旗舰店</x:v>
+      </x:c>
+      <x:c r="K92" s="184"/>
+      <x:c r="L92" s="184"/>
+      <x:c r="M92" s="184"/>
+      <x:c r="N92" s="184"/>
+      <x:c r="O92" s="184"/>
+      <x:c r="P92" s="193" t="str">
+        <x:v>2026-08-28</x:v>
+      </x:c>
+      <x:c r="Q92" s="193" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="R92" s="187" t="str">
+        <x:v>先用后付；确认收货后应付5.36元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" ht="48" customHeight="1">
+      <x:c r="A93" s="185" t="str">
+        <x:v>ZC-20260830-001</x:v>
+      </x:c>
+      <x:c r="B93" s="185" t="str">
+        <x:v>材料耗材</x:v>
+      </x:c>
+      <x:c r="C93" s="185" t="str">
+        <x:v>低值易耗品</x:v>
+      </x:c>
+      <x:c r="D93" s="188" t="str">
+        <x:v>绿林高纯度焊锡丝</x:v>
+      </x:c>
+      <x:c r="E93" s="188" t="str">
+        <x:v>锡含量63% / 0.8mm / 50g / 自带松香</x:v>
+      </x:c>
+      <x:c r="F93" s="191" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G93" s="197" t="n">
+        <x:v>15.8</x:v>
+      </x:c>
+      <x:c r="H93" s="197" t="n">
+        <x:v>31.6</x:v>
+      </x:c>
+      <x:c r="I93" s="200" t="n">
+        <x:v>46264</x:v>
+      </x:c>
+      <x:c r="J93" s="188" t="str">
+        <x:v>绿林官方旗舰店</x:v>
+      </x:c>
+      <x:c r="K93" s="185"/>
+      <x:c r="L93" s="185"/>
+      <x:c r="M93" s="185"/>
+      <x:c r="N93" s="185"/>
+      <x:c r="O93" s="185"/>
+      <x:c r="P93" s="194" t="str">
+        <x:v>2026-08-30</x:v>
+      </x:c>
+      <x:c r="Q93" s="194" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="R93" s="188" t="str">
+        <x:v>先用后付；确认收货后应付31.60元；63%焊锡不等同BOM要求的无铅低温锡丝</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4772,7 +5229,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R40c134a449a5490b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4efbe8266f2f40cd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4822,16 +5279,16 @@
         <x:v>材料耗材</x:v>
       </x:c>
       <x:c r="B5" s="80" t="n">
-        <x:f>COUNTIF('资产清单'!$B$7:$B$86,A5)</x:f>
-        <x:v>43</x:v>
+        <x:f>COUNTIF('资产清单'!$B$7:$B$93,A5)</x:f>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C5" s="80" t="n">
-        <x:f>SUMIF('资产清单'!$B$7:$B$86,A5,'资产清单'!$F$7:$F$86)</x:f>
-        <x:v>71</x:v>
+        <x:f>SUMIF('资产清单'!$B$7:$B$93,A5,'资产清单'!$F$7:$F$93)</x:f>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D5" s="82" t="n">
-        <x:f>SUMIF('资产清单'!$B$7:$B$86,A5,'资产清单'!$H$7:$H$86)</x:f>
-        <x:v>663.5200000000002</x:v>
+        <x:f>SUMIF('资产清单'!$B$7:$B$93,A5,'资产清单'!$H$7:$H$93)</x:f>
+        <x:v>824.4800000000002</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="28" customHeight="1">
@@ -4839,15 +5296,15 @@
         <x:v>电子元器件</x:v>
       </x:c>
       <x:c r="B6" s="80" t="n">
-        <x:f>COUNTIF('资产清单'!$B$7:$B$86,A6)</x:f>
+        <x:f>COUNTIF('资产清单'!$B$7:$B$93,A6)</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="C6" s="80" t="n">
-        <x:f>SUMIF('资产清单'!$B$7:$B$86,A6,'资产清单'!$F$7:$F$86)</x:f>
+        <x:f>SUMIF('资产清单'!$B$7:$B$93,A6,'资产清单'!$F$7:$F$93)</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="D6" s="82" t="n">
-        <x:f>SUMIF('资产清单'!$B$7:$B$86,A6,'资产清单'!$H$7:$H$86)</x:f>
+        <x:f>SUMIF('资产清单'!$B$7:$B$93,A6,'资产清单'!$H$7:$H$93)</x:f>
         <x:v>300.73</x:v>
       </x:c>
     </x:row>
@@ -4856,16 +5313,16 @@
         <x:v>工具器具</x:v>
       </x:c>
       <x:c r="B7" s="80" t="n">
-        <x:f>COUNTIF('资产清单'!$B$7:$B$86,A7)</x:f>
-        <x:v>9</x:v>
+        <x:f>COUNTIF('资产清单'!$B$7:$B$93,A7)</x:f>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C7" s="80" t="n">
-        <x:f>SUMIF('资产清单'!$B$7:$B$86,A7,'资产清单'!$F$7:$F$86)</x:f>
-        <x:v>9</x:v>
+        <x:f>SUMIF('资产清单'!$B$7:$B$93,A7,'资产清单'!$F$7:$F$93)</x:f>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D7" s="82" t="n">
-        <x:f>SUMIF('资产清单'!$B$7:$B$86,A7,'资产清单'!$H$7:$H$86)</x:f>
-        <x:v>374.87</x:v>
+        <x:f>SUMIF('资产清单'!$B$7:$B$93,A7,'资产清单'!$H$7:$H$93)</x:f>
+        <x:v>419.87</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="28" customHeight="1">
@@ -4873,16 +5330,16 @@
         <x:v>设备及装置</x:v>
       </x:c>
       <x:c r="B8" s="80" t="n">
-        <x:f>COUNTIF('资产清单'!$B$7:$B$86,A8)</x:f>
-        <x:v>15</x:v>
+        <x:f>COUNTIF('资产清单'!$B$7:$B$93,A8)</x:f>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C8" s="80" t="n">
-        <x:f>SUMIF('资产清单'!$B$7:$B$86,A8,'资产清单'!$F$7:$F$86)</x:f>
-        <x:v>19</x:v>
+        <x:f>SUMIF('资产清单'!$B$7:$B$93,A8,'资产清单'!$F$7:$F$93)</x:f>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D8" s="82" t="n">
-        <x:f>SUMIF('资产清单'!$B$7:$B$86,A8,'资产清单'!$H$7:$H$86)</x:f>
-        <x:v>6867.01</x:v>
+        <x:f>SUMIF('资产清单'!$B$7:$B$93,A8,'资产清单'!$H$7:$H$93)</x:f>
+        <x:v>7281.01</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="28" customHeight="1">
@@ -4890,15 +5347,15 @@
         <x:v>仪器仪表</x:v>
       </x:c>
       <x:c r="B9" s="80" t="n">
-        <x:f>COUNTIF('资产清单'!$B$7:$B$86,A9)</x:f>
+        <x:f>COUNTIF('资产清单'!$B$7:$B$93,A9)</x:f>
         <x:v>3</x:v>
       </x:c>
       <x:c r="C9" s="80" t="n">
-        <x:f>SUMIF('资产清单'!$B$7:$B$86,A9,'资产清单'!$F$7:$F$86)</x:f>
+        <x:f>SUMIF('资产清单'!$B$7:$B$93,A9,'资产清单'!$F$7:$F$93)</x:f>
         <x:v>3</x:v>
       </x:c>
       <x:c r="D9" s="82" t="n">
-        <x:f>SUMIF('资产清单'!$B$7:$B$86,A9,'资产清单'!$H$7:$H$86)</x:f>
+        <x:f>SUMIF('资产清单'!$B$7:$B$93,A9,'资产清单'!$H$7:$H$93)</x:f>
         <x:v>320.6</x:v>
       </x:c>
     </x:row>
@@ -4908,15 +5365,15 @@
       </x:c>
       <x:c r="B10" s="81" t="n">
         <x:f>SUM(B5:B9)</x:f>
-        <x:v>80</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C10" s="81" t="n">
         <x:f>SUM(C5:C9)</x:f>
-        <x:v>112</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D10" s="83" t="n">
         <x:f>SUM(D5:D9)</x:f>
-        <x:v>8526.730000000001</x:v>
+        <x:v>9146.69</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5097,71 +5554,147 @@
         <x:v>分电板订单：实付款102.50元=商品97.50元+运费5.00元</x:v>
       </x:c>
     </x:row>
-    <x:row r="10">
-      <x:c r="A10" t="str">
-        <x:v>费用合计</x:v>
-      </x:c>
-      <x:c r="B10"/>
-      <x:c r="C10" s="90" t="n">
-        <x:f>SUM(C5:C9)</x:f>
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="D10"/>
-      <x:c r="E10"/>
-      <x:c r="F10"/>
-      <x:c r="G10"/>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="11" t="str">
-        <x:v>勾稽项目</x:v>
-      </x:c>
-      <x:c r="B11" s="11" t="str">
-        <x:v>金额（元）</x:v>
+    <x:row r="10" ht="36" customHeight="1">
+      <x:c r="A10" s="227" t="n">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="B10" s="229" t="str">
+        <x:v>运费</x:v>
+      </x:c>
+      <x:c r="C10" s="231" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D10" s="229" t="str">
+        <x:v>VIOCEAN海目云海洋科技企业店</x:v>
+      </x:c>
+      <x:c r="E10" s="229" t="str">
+        <x:v>2026-08-28</x:v>
+      </x:c>
+      <x:c r="F10" s="229" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G10" s="229" t="str">
+        <x:v>用户确认：VIOCEAN订单10.00元差额为运费</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="36" customHeight="1">
+      <x:c r="A11" s="228" t="n">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="B11" s="230" t="str">
+        <x:v>运费</x:v>
+      </x:c>
+      <x:c r="C11" s="232" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D11" s="233" t="str">
+        <x:v>EXOCEAN拓洲智能</x:v>
+      </x:c>
+      <x:c r="E11" s="233" t="str">
+        <x:v>2026-08-28</x:v>
+      </x:c>
+      <x:c r="F11" s="233" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G11" s="233" t="str">
+        <x:v>用户确认：EXOCEAN订单12.00元差额为运费</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" t="str">
-        <x:v>实物资产原值</x:v>
-      </x:c>
-      <x:c r="B12" s="90" t="n">
-        <x:f>'资产清单'!N3</x:f>
-        <x:v>8526.73</x:v>
-      </x:c>
+        <x:v>费用合计</x:v>
+      </x:c>
+      <x:c r="B12" s="90"/>
+      <x:c r="C12" t="n">
+        <x:f>SUM(C5:C11)</x:f>
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D12"/>
+      <x:c r="E12"/>
+      <x:c r="F12"/>
+      <x:c r="G12"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" t="str">
-        <x:v>未纳入费用</x:v>
-      </x:c>
-      <x:c r="B13" s="90" t="n">
-        <x:f>C10</x:f>
-        <x:v>63</x:v>
-      </x:c>
+        <x:v>勾稽项目</x:v>
+      </x:c>
+      <x:c r="B13" s="90" t="str">
+        <x:v>金额（元）</x:v>
+      </x:c>
+      <x:c r="C13"/>
+      <x:c r="D13"/>
+      <x:c r="E13"/>
+      <x:c r="F13"/>
+      <x:c r="G13"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" t="str">
-        <x:v>勾稽采购总额</x:v>
+        <x:v>实物资产原值</x:v>
       </x:c>
       <x:c r="B14" s="90" t="n">
-        <x:f>B12+B13</x:f>
-        <x:v>8589.73</x:v>
-      </x:c>
+        <x:f>'分类汇总'!D10</x:f>
+        <x:v>9146.69</x:v>
+      </x:c>
+      <x:c r="C14"/>
+      <x:c r="D14"/>
+      <x:c r="E14"/>
+      <x:c r="F14"/>
+      <x:c r="G14"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" t="str">
-        <x:v>原采购总额</x:v>
+        <x:v>未纳入费用</x:v>
       </x:c>
       <x:c r="B15" s="90" t="n">
-        <x:v>8589.73</x:v>
-      </x:c>
+        <x:f>C12</x:f>
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="C15"/>
+      <x:c r="D15"/>
+      <x:c r="E15"/>
+      <x:c r="F15"/>
+      <x:c r="G15"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="76" t="str">
+        <x:v>勾稽采购总额</x:v>
+      </x:c>
+      <x:c r="B16" s="91" t="n">
+        <x:f>B14+B15</x:f>
+        <x:v>9231.69</x:v>
+      </x:c>
+      <x:c r="C16"/>
+      <x:c r="D16"/>
+      <x:c r="E16"/>
+      <x:c r="F16"/>
+      <x:c r="G16"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>原采购总额</x:v>
+      </x:c>
+      <x:c r="B17" s="90" t="n">
+        <x:v>9231.69</x:v>
+      </x:c>
+      <x:c r="C17"/>
+      <x:c r="D17"/>
+      <x:c r="E17"/>
+      <x:c r="F17"/>
+      <x:c r="G17"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
         <x:v>差额</x:v>
       </x:c>
-      <x:c r="B16" s="91" t="n">
-        <x:f>B14-B15</x:f>
+      <x:c r="B18" s="90" t="n">
+        <x:f>B16-B17</x:f>
         <x:v>0</x:v>
       </x:c>
+      <x:c r="C18"/>
+      <x:c r="D18"/>
+      <x:c r="E18"/>
+      <x:c r="F18"/>
+      <x:c r="G18"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/物资/资产清单.xlsx
+++ b/物资/资产清单.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产清单" sheetId="1" r:id="R4768592e950644a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类汇总" sheetId="2" r:id="R57a8495103d24375"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="未纳入资产" sheetId="3" r:id="R91bbb4e5f852463f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产清单" sheetId="1" r:id="Rb76de1b5afd44a1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类汇总" sheetId="2" r:id="R3578ef2d8b6f494e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="未纳入资产" sheetId="3" r:id="Reb4e7eb0adfa49c9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -15,11 +15,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="4">
+  <x:numFmts count="5">
     <x:numFmt numFmtId="200" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="201" formatCode="#,##0"/>
     <x:numFmt numFmtId="202" formatCode="yyyy-mm-dd"/>
     <x:numFmt numFmtId="203" formatCode="0"/>
+    <x:numFmt numFmtId="204" formatCode="#,##0.000"/>
   </x:numFmts>
   <x:fonts count="15">
     <x:font>
@@ -106,7 +107,7 @@
       <x:name val="Microsoft YaHei"/>
     </x:font>
   </x:fonts>
-  <x:fills count="19">
+  <x:fills count="23">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -198,6 +199,26 @@
         <x:fgColor rgb="FFFFFFFF"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="8">
     <x:border/>
@@ -270,7 +291,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="234">
+  <x:cellXfs count="277">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -829,6 +850,135 @@
     <x:xf numFmtId="0" fontId="13" fillId="18" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="12" fillId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="12" fillId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="12" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="12" fillId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="12" fillId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="12" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="12" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="12" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="12" fillId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="12" fillId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="12" fillId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="12" fillId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="21" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="21" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="12" fillId="21" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="12" fillId="21" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="21" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="21" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="12" fillId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -837,8 +987,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AssetsTable" displayName="AssetsTable" ref="A6:R93" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A6:R93"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AssetsTable" displayName="AssetsTable" ref="A6:R102" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A6:R102"/>
   <x:tableColumns count="18">
     <x:tableColumn id="1" name="资产编号"/>
     <x:tableColumn id="2" name="管理类别"/>
@@ -1129,8 +1279,8 @@
       <x:c r="B3" s="19"/>
       <x:c r="C3" s="20"/>
       <x:c r="D3" s="27" t="n">
-        <x:f>COUNTA(A7:A93)</x:f>
-        <x:v>87</x:v>
+        <x:f>COUNTA(A7:A102)</x:f>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E3" s="28"/>
       <x:c r="F3" s="18" t="str">
@@ -1139,8 +1289,8 @@
       <x:c r="G3" s="19"/>
       <x:c r="H3" s="20"/>
       <x:c r="I3" s="27" t="n">
-        <x:f>SUM(F7:F93)</x:f>
-        <x:v>124</x:v>
+        <x:f>SUM(F7:F102)</x:f>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="J3" s="28"/>
       <x:c r="K3" s="18" t="str">
@@ -1149,8 +1299,8 @@
       <x:c r="L3" s="19"/>
       <x:c r="M3" s="20"/>
       <x:c r="N3" s="32" t="n">
-        <x:f>SUM(H7:H93)</x:f>
-        <x:v>9146.69</x:v>
+        <x:f>SUM(H7:H102)</x:f>
+        <x:v>9311.88</x:v>
       </x:c>
       <x:c r="O3" s="33"/>
       <x:c r="P3" s="33"/>
@@ -5203,6 +5353,420 @@
       </x:c>
       <x:c r="R93" s="188" t="str">
         <x:v>先用后付；确认收货后应付31.60元；63%焊锡不等同BOM要求的无铅低温锡丝</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" ht="48" customHeight="1">
+      <x:c r="A94" s="258" t="str">
+        <x:v>ZC-20260901-001</x:v>
+      </x:c>
+      <x:c r="B94" s="258" t="str">
+        <x:v>工具器具</x:v>
+      </x:c>
+      <x:c r="C94" s="258" t="str">
+        <x:v>可周转资产</x:v>
+      </x:c>
+      <x:c r="D94" s="273" t="str">
+        <x:v>15件套充电式电动螺丝刀</x:v>
+      </x:c>
+      <x:c r="E94" s="273" t="str">
+        <x:v>15件套 / 充电式 / 手持电钻螺丝刀</x:v>
+      </x:c>
+      <x:c r="F94" s="259" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G94" s="260" t="n">
+        <x:v>27.84</x:v>
+      </x:c>
+      <x:c r="H94" s="260" t="n">
+        <x:v>27.84</x:v>
+      </x:c>
+      <x:c r="I94" s="261" t="n">
+        <x:v>46266</x:v>
+      </x:c>
+      <x:c r="J94" s="273" t="str">
+        <x:v>鲸选坐标超市（西丽店）</x:v>
+      </x:c>
+      <x:c r="K94" s="258"/>
+      <x:c r="L94" s="258"/>
+      <x:c r="M94" s="258"/>
+      <x:c r="N94" s="258"/>
+      <x:c r="O94" s="258"/>
+      <x:c r="P94" s="262" t="str">
+        <x:v>2026-09-01</x:v>
+      </x:c>
+      <x:c r="Q94" s="262" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="R94" s="273" t="str">
+        <x:v>订单已送达；截图实付27.84元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" ht="48" customHeight="1">
+      <x:c r="A95" s="263" t="str">
+        <x:v>ZC-20260901-002</x:v>
+      </x:c>
+      <x:c r="B95" s="263" t="str">
+        <x:v>材料耗材</x:v>
+      </x:c>
+      <x:c r="C95" s="263" t="str">
+        <x:v>低值易耗品</x:v>
+      </x:c>
+      <x:c r="D95" s="274" t="str">
+        <x:v>75%酒精消毒湿巾</x:v>
+      </x:c>
+      <x:c r="E95" s="274" t="str">
+        <x:v>带盖大包 / 75%酒精</x:v>
+      </x:c>
+      <x:c r="F95" s="264" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G95" s="265" t="n">
+        <x:v>5.97</x:v>
+      </x:c>
+      <x:c r="H95" s="265" t="n">
+        <x:v>5.97</x:v>
+      </x:c>
+      <x:c r="I95" s="266" t="n">
+        <x:v>46266</x:v>
+      </x:c>
+      <x:c r="J95" s="274" t="str">
+        <x:v>鲸选坐标超市（西丽店）</x:v>
+      </x:c>
+      <x:c r="K95" s="263"/>
+      <x:c r="L95" s="263"/>
+      <x:c r="M95" s="263"/>
+      <x:c r="N95" s="263"/>
+      <x:c r="O95" s="263"/>
+      <x:c r="P95" s="267" t="str">
+        <x:v>2026-09-01</x:v>
+      </x:c>
+      <x:c r="Q95" s="267" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="R95" s="274" t="str">
+        <x:v>订单已送达；截图实付5.97元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" ht="48" customHeight="1">
+      <x:c r="A96" s="258" t="str">
+        <x:v>ZC-20260901-003</x:v>
+      </x:c>
+      <x:c r="B96" s="258" t="str">
+        <x:v>材料耗材</x:v>
+      </x:c>
+      <x:c r="C96" s="258" t="str">
+        <x:v>低值易耗品</x:v>
+      </x:c>
+      <x:c r="D96" s="273" t="str">
+        <x:v>公牛PVC电工绝缘胶带</x:v>
+      </x:c>
+      <x:c r="E96" s="273" t="str">
+        <x:v>黑色 / 9米/卷 / 阻燃耐低温</x:v>
+      </x:c>
+      <x:c r="F96" s="259" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G96" s="260" t="n">
+        <x:v>3.02</x:v>
+      </x:c>
+      <x:c r="H96" s="260" t="n">
+        <x:v>3.02</x:v>
+      </x:c>
+      <x:c r="I96" s="261" t="n">
+        <x:v>46266</x:v>
+      </x:c>
+      <x:c r="J96" s="273" t="str">
+        <x:v>鲸选坐标超市（西丽店）</x:v>
+      </x:c>
+      <x:c r="K96" s="258"/>
+      <x:c r="L96" s="258"/>
+      <x:c r="M96" s="258"/>
+      <x:c r="N96" s="258"/>
+      <x:c r="O96" s="258"/>
+      <x:c r="P96" s="262" t="str">
+        <x:v>2026-09-01</x:v>
+      </x:c>
+      <x:c r="Q96" s="262" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="R96" s="273" t="str">
+        <x:v>订单已送达；截图实付3.02元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" ht="48" customHeight="1">
+      <x:c r="A97" s="263" t="str">
+        <x:v>ZC-20260901-004</x:v>
+      </x:c>
+      <x:c r="B97" s="263" t="str">
+        <x:v>材料耗材</x:v>
+      </x:c>
+      <x:c r="C97" s="263" t="str">
+        <x:v>低值易耗品</x:v>
+      </x:c>
+      <x:c r="D97" s="274" t="str">
+        <x:v>鹰牌水磨砂纸</x:v>
+      </x:c>
+      <x:c r="E97" s="274" t="str">
+        <x:v>150目</x:v>
+      </x:c>
+      <x:c r="F97" s="264" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G97" s="276" t="n">
+        <x:v>1.194</x:v>
+      </x:c>
+      <x:c r="H97" s="265" t="n">
+        <x:v>5.97</x:v>
+      </x:c>
+      <x:c r="I97" s="266" t="n">
+        <x:v>46266</x:v>
+      </x:c>
+      <x:c r="J97" s="274" t="str">
+        <x:v>鲸选坐标超市（西丽店）</x:v>
+      </x:c>
+      <x:c r="K97" s="263"/>
+      <x:c r="L97" s="263"/>
+      <x:c r="M97" s="263"/>
+      <x:c r="N97" s="263"/>
+      <x:c r="O97" s="263"/>
+      <x:c r="P97" s="267" t="str">
+        <x:v>2026-09-01</x:v>
+      </x:c>
+      <x:c r="Q97" s="267" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="R97" s="274" t="str">
+        <x:v>订单已送达；5张合计5.97元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" ht="48" customHeight="1">
+      <x:c r="A98" s="268" t="str">
+        <x:v>ZC-20260902-001</x:v>
+      </x:c>
+      <x:c r="B98" s="268" t="str">
+        <x:v>电子元器件</x:v>
+      </x:c>
+      <x:c r="C98" s="268" t="str">
+        <x:v>项目组件</x:v>
+      </x:c>
+      <x:c r="D98" s="275" t="str">
+        <x:v>XT60并联转接头</x:v>
+      </x:c>
+      <x:c r="E98" s="275" t="str">
+        <x:v>XT60 两母一公</x:v>
+      </x:c>
+      <x:c r="F98" s="269" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G98" s="270" t="n">
+        <x:v>10.4</x:v>
+      </x:c>
+      <x:c r="H98" s="270" t="n">
+        <x:v>10.4</x:v>
+      </x:c>
+      <x:c r="I98" s="271" t="n">
+        <x:v>46267</x:v>
+      </x:c>
+      <x:c r="J98" s="275" t="str">
+        <x:v>亿恒电子888</x:v>
+      </x:c>
+      <x:c r="K98" s="268"/>
+      <x:c r="L98" s="268"/>
+      <x:c r="M98" s="268"/>
+      <x:c r="N98" s="268"/>
+      <x:c r="O98" s="268"/>
+      <x:c r="P98" s="272" t="str">
+        <x:v>2026-09-02</x:v>
+      </x:c>
+      <x:c r="Q98" s="272" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="R98" s="275" t="str">
+        <x:v>订单号33163934900009008294；已发货</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" ht="48" customHeight="1">
+      <x:c r="A99" s="263" t="str">
+        <x:v>ZC-20260902-002</x:v>
+      </x:c>
+      <x:c r="B99" s="263" t="str">
+        <x:v>电子元器件</x:v>
+      </x:c>
+      <x:c r="C99" s="263" t="str">
+        <x:v>项目组件</x:v>
+      </x:c>
+      <x:c r="D99" s="274" t="str">
+        <x:v>XT90公母头延长转接线</x:v>
+      </x:c>
+      <x:c r="E99" s="274" t="str">
+        <x:v>XT90公头转母头 / 10号线 / 30cm</x:v>
+      </x:c>
+      <x:c r="F99" s="264" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G99" s="265" t="n">
+        <x:v>15.7</x:v>
+      </x:c>
+      <x:c r="H99" s="265" t="n">
+        <x:v>15.7</x:v>
+      </x:c>
+      <x:c r="I99" s="266" t="n">
+        <x:v>46267</x:v>
+      </x:c>
+      <x:c r="J99" s="274" t="str">
+        <x:v>亿恒电子888</x:v>
+      </x:c>
+      <x:c r="K99" s="263"/>
+      <x:c r="L99" s="263"/>
+      <x:c r="M99" s="263"/>
+      <x:c r="N99" s="263"/>
+      <x:c r="O99" s="263"/>
+      <x:c r="P99" s="267" t="str">
+        <x:v>2026-09-02</x:v>
+      </x:c>
+      <x:c r="Q99" s="267" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="R99" s="274" t="str">
+        <x:v>订单号33163934900009008294；已发货</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" ht="48" customHeight="1">
+      <x:c r="A100" s="258" t="str">
+        <x:v>ZC-20260902-003</x:v>
+      </x:c>
+      <x:c r="B100" s="258" t="str">
+        <x:v>电子元器件</x:v>
+      </x:c>
+      <x:c r="C100" s="258" t="str">
+        <x:v>项目组件</x:v>
+      </x:c>
+      <x:c r="D100" s="273" t="str">
+        <x:v>4S平衡充电延长线（第1条）</x:v>
+      </x:c>
+      <x:c r="E100" s="273" t="str">
+        <x:v>4S（5线）/ 22AWG / 公转母 / 10cm</x:v>
+      </x:c>
+      <x:c r="F100" s="259" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G100" s="260" t="n">
+        <x:v>2.9</x:v>
+      </x:c>
+      <x:c r="H100" s="260" t="n">
+        <x:v>2.9</x:v>
+      </x:c>
+      <x:c r="I100" s="261" t="n">
+        <x:v>46267</x:v>
+      </x:c>
+      <x:c r="J100" s="273" t="str">
+        <x:v>尼莱电子</x:v>
+      </x:c>
+      <x:c r="K100" s="258"/>
+      <x:c r="L100" s="258"/>
+      <x:c r="M100" s="258"/>
+      <x:c r="N100" s="258"/>
+      <x:c r="O100" s="258"/>
+      <x:c r="P100" s="262" t="str">
+        <x:v>2026-09-02</x:v>
+      </x:c>
+      <x:c r="Q100" s="262" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="R100" s="273" t="str">
+        <x:v>订单号33163934900009053486；待发货</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" ht="48" customHeight="1">
+      <x:c r="A101" s="263" t="str">
+        <x:v>ZC-20260902-004</x:v>
+      </x:c>
+      <x:c r="B101" s="263" t="str">
+        <x:v>电子元器件</x:v>
+      </x:c>
+      <x:c r="C101" s="263" t="str">
+        <x:v>项目组件</x:v>
+      </x:c>
+      <x:c r="D101" s="274" t="str">
+        <x:v>4S平衡充电延长线（第2条）</x:v>
+      </x:c>
+      <x:c r="E101" s="274" t="str">
+        <x:v>4S（5线）/ 22AWG / 公转母 / 10cm</x:v>
+      </x:c>
+      <x:c r="F101" s="264" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G101" s="265" t="n">
+        <x:v>3.4</x:v>
+      </x:c>
+      <x:c r="H101" s="265" t="n">
+        <x:v>3.4</x:v>
+      </x:c>
+      <x:c r="I101" s="266" t="n">
+        <x:v>46267</x:v>
+      </x:c>
+      <x:c r="J101" s="274" t="str">
+        <x:v>尼莱电子</x:v>
+      </x:c>
+      <x:c r="K101" s="263"/>
+      <x:c r="L101" s="263"/>
+      <x:c r="M101" s="263"/>
+      <x:c r="N101" s="263"/>
+      <x:c r="O101" s="263"/>
+      <x:c r="P101" s="267" t="str">
+        <x:v>2026-09-02</x:v>
+      </x:c>
+      <x:c r="Q101" s="267" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="R101" s="274" t="str">
+        <x:v>截图所示规格文字相同，按订单第2条单列；待发货</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" ht="48" customHeight="1">
+      <x:c r="A102" s="268" t="str">
+        <x:v>ZC-20260902-005</x:v>
+      </x:c>
+      <x:c r="B102" s="268" t="str">
+        <x:v>设备及装置</x:v>
+      </x:c>
+      <x:c r="C102" s="268" t="str">
+        <x:v>可周转资产</x:v>
+      </x:c>
+      <x:c r="D102" s="275" t="str">
+        <x:v>IMAX B6AC 80W平衡充电器</x:v>
+      </x:c>
+      <x:c r="E102" s="275" t="str">
+        <x:v>B6AC+XT90线 / 内置电源 / 80W</x:v>
+      </x:c>
+      <x:c r="F102" s="269" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G102" s="270" t="n">
+        <x:v>89.99</x:v>
+      </x:c>
+      <x:c r="H102" s="270" t="n">
+        <x:v>89.99</x:v>
+      </x:c>
+      <x:c r="I102" s="271" t="n">
+        <x:v>46267</x:v>
+      </x:c>
+      <x:c r="J102" s="275" t="str">
+        <x:v>星星模型配件</x:v>
+      </x:c>
+      <x:c r="K102" s="268"/>
+      <x:c r="L102" s="268"/>
+      <x:c r="M102" s="268"/>
+      <x:c r="N102" s="268"/>
+      <x:c r="O102" s="268"/>
+      <x:c r="P102" s="272" t="str">
+        <x:v>2026-09-02</x:v>
+      </x:c>
+      <x:c r="Q102" s="272" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="R102" s="275" t="str">
+        <x:v>订单号33163934900009099495；已发货</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5229,7 +5793,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4efbe8266f2f40cd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R535d0410db964a23"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5279,16 +5843,16 @@
         <x:v>材料耗材</x:v>
       </x:c>
       <x:c r="B5" s="80" t="n">
-        <x:f>COUNTIF('资产清单'!$B$7:$B$93,A5)</x:f>
-        <x:v>47</x:v>
+        <x:f>COUNTIF('资产清单'!$B$7:$B$102,A5)</x:f>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C5" s="80" t="n">
-        <x:f>SUMIF('资产清单'!$B$7:$B$93,A5,'资产清单'!$F$7:$F$93)</x:f>
-        <x:v>76</x:v>
+        <x:f>SUMIF('资产清单'!$B$7:$B$102,A5,'资产清单'!$F$7:$F$102)</x:f>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D5" s="82" t="n">
-        <x:f>SUMIF('资产清单'!$B$7:$B$93,A5,'资产清单'!$H$7:$H$93)</x:f>
-        <x:v>824.4800000000002</x:v>
+        <x:f>SUMIF('资产清单'!$B$7:$B$102,A5,'资产清单'!$H$7:$H$102)</x:f>
+        <x:v>839.4400000000003</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="28" customHeight="1">
@@ -5296,16 +5860,16 @@
         <x:v>电子元器件</x:v>
       </x:c>
       <x:c r="B6" s="80" t="n">
-        <x:f>COUNTIF('资产清单'!$B$7:$B$93,A6)</x:f>
-        <x:v>10</x:v>
+        <x:f>COUNTIF('资产清单'!$B$7:$B$102,A6)</x:f>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C6" s="80" t="n">
-        <x:f>SUMIF('资产清单'!$B$7:$B$93,A6,'资产清单'!$F$7:$F$93)</x:f>
-        <x:v>10</x:v>
+        <x:f>SUMIF('资产清单'!$B$7:$B$102,A6,'资产清单'!$F$7:$F$102)</x:f>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D6" s="82" t="n">
-        <x:f>SUMIF('资产清单'!$B$7:$B$93,A6,'资产清单'!$H$7:$H$93)</x:f>
-        <x:v>300.73</x:v>
+        <x:f>SUMIF('资产清单'!$B$7:$B$102,A6,'资产清单'!$H$7:$H$102)</x:f>
+        <x:v>333.12999999999994</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="28" customHeight="1">
@@ -5313,16 +5877,16 @@
         <x:v>工具器具</x:v>
       </x:c>
       <x:c r="B7" s="80" t="n">
-        <x:f>COUNTIF('资产清单'!$B$7:$B$93,A7)</x:f>
-        <x:v>10</x:v>
+        <x:f>COUNTIF('资产清单'!$B$7:$B$102,A7)</x:f>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C7" s="80" t="n">
-        <x:f>SUMIF('资产清单'!$B$7:$B$93,A7,'资产清单'!$F$7:$F$93)</x:f>
-        <x:v>10</x:v>
+        <x:f>SUMIF('资产清单'!$B$7:$B$102,A7,'资产清单'!$F$7:$F$102)</x:f>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D7" s="82" t="n">
-        <x:f>SUMIF('资产清单'!$B$7:$B$93,A7,'资产清单'!$H$7:$H$93)</x:f>
-        <x:v>419.87</x:v>
+        <x:f>SUMIF('资产清单'!$B$7:$B$102,A7,'资产清单'!$H$7:$H$102)</x:f>
+        <x:v>447.71</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="28" customHeight="1">
@@ -5330,16 +5894,16 @@
         <x:v>设备及装置</x:v>
       </x:c>
       <x:c r="B8" s="80" t="n">
-        <x:f>COUNTIF('资产清单'!$B$7:$B$93,A8)</x:f>
-        <x:v>17</x:v>
+        <x:f>COUNTIF('资产清单'!$B$7:$B$102,A8)</x:f>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C8" s="80" t="n">
-        <x:f>SUMIF('资产清单'!$B$7:$B$93,A8,'资产清单'!$F$7:$F$93)</x:f>
-        <x:v>25</x:v>
+        <x:f>SUMIF('资产清单'!$B$7:$B$102,A8,'资产清单'!$F$7:$F$102)</x:f>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D8" s="82" t="n">
-        <x:f>SUMIF('资产清单'!$B$7:$B$93,A8,'资产清单'!$H$7:$H$93)</x:f>
-        <x:v>7281.01</x:v>
+        <x:f>SUMIF('资产清单'!$B$7:$B$102,A8,'资产清单'!$H$7:$H$102)</x:f>
+        <x:v>7371</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="28" customHeight="1">
@@ -5347,15 +5911,15 @@
         <x:v>仪器仪表</x:v>
       </x:c>
       <x:c r="B9" s="80" t="n">
-        <x:f>COUNTIF('资产清单'!$B$7:$B$93,A9)</x:f>
+        <x:f>COUNTIF('资产清单'!$B$7:$B$102,A9)</x:f>
         <x:v>3</x:v>
       </x:c>
       <x:c r="C9" s="80" t="n">
-        <x:f>SUMIF('资产清单'!$B$7:$B$93,A9,'资产清单'!$F$7:$F$93)</x:f>
+        <x:f>SUMIF('资产清单'!$B$7:$B$102,A9,'资产清单'!$F$7:$F$102)</x:f>
         <x:v>3</x:v>
       </x:c>
       <x:c r="D9" s="82" t="n">
-        <x:f>SUMIF('资产清单'!$B$7:$B$93,A9,'资产清单'!$H$7:$H$93)</x:f>
+        <x:f>SUMIF('资产清单'!$B$7:$B$102,A9,'资产清单'!$H$7:$H$102)</x:f>
         <x:v>320.6</x:v>
       </x:c>
     </x:row>
@@ -5365,15 +5929,15 @@
       </x:c>
       <x:c r="B10" s="81" t="n">
         <x:f>SUM(B5:B9)</x:f>
-        <x:v>87</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C10" s="81" t="n">
         <x:f>SUM(C5:C9)</x:f>
-        <x:v>124</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="D10" s="83" t="n">
         <x:f>SUM(D5:D9)</x:f>
-        <x:v>9146.69</x:v>
+        <x:v>9311.880000000001</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5601,27 +6165,37 @@
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" t="str">
-        <x:v>费用合计</x:v>
-      </x:c>
-      <x:c r="B12" s="90"/>
-      <x:c r="C12" t="n">
-        <x:f>SUM(C5:C11)</x:f>
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="D12"/>
-      <x:c r="E12"/>
-      <x:c r="F12"/>
-      <x:c r="G12"/>
+      <x:c r="A12" s="201" t="n">
+        <x:v>46267</x:v>
+      </x:c>
+      <x:c r="B12" s="90" t="str">
+        <x:v>运费</x:v>
+      </x:c>
+      <x:c r="C12" s="90" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D12" t="str">
+        <x:v>尼莱电子</x:v>
+      </x:c>
+      <x:c r="E12" t="str">
+        <x:v>2026-09-02</x:v>
+      </x:c>
+      <x:c r="F12" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G12" t="str">
+        <x:v>商品合计6.30元+运费6.00元=实付12.30元</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" t="str">
-        <x:v>勾稽项目</x:v>
-      </x:c>
-      <x:c r="B13" s="90" t="str">
-        <x:v>金额（元）</x:v>
-      </x:c>
-      <x:c r="C13"/>
+        <x:v>费用合计</x:v>
+      </x:c>
+      <x:c r="B13" s="90"/>
+      <x:c r="C13" t="n">
+        <x:f>SUM(C5:C12)</x:f>
+        <x:v>91</x:v>
+      </x:c>
       <x:c r="D13"/>
       <x:c r="E13"/>
       <x:c r="F13"/>
@@ -5629,11 +6203,10 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" t="str">
-        <x:v>实物资产原值</x:v>
-      </x:c>
-      <x:c r="B14" s="90" t="n">
-        <x:f>'分类汇总'!D10</x:f>
-        <x:v>9146.69</x:v>
+        <x:v>勾稽项目</x:v>
+      </x:c>
+      <x:c r="B14" s="90" t="str">
+        <x:v>金额（元）</x:v>
       </x:c>
       <x:c r="C14"/>
       <x:c r="D14"/>
@@ -5643,11 +6216,11 @@
     </x:row>
     <x:row r="15">
       <x:c r="A15" t="str">
-        <x:v>未纳入费用</x:v>
+        <x:v>实物资产原值</x:v>
       </x:c>
       <x:c r="B15" s="90" t="n">
-        <x:f>C12</x:f>
-        <x:v>85</x:v>
+        <x:f>'分类汇总'!D10</x:f>
+        <x:v>9311.880000000001</x:v>
       </x:c>
       <x:c r="C15"/>
       <x:c r="D15"/>
@@ -5657,11 +6230,11 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="76" t="str">
-        <x:v>勾稽采购总额</x:v>
+        <x:v>未纳入费用</x:v>
       </x:c>
       <x:c r="B16" s="91" t="n">
-        <x:f>B14+B15</x:f>
-        <x:v>9231.69</x:v>
+        <x:f>C13</x:f>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C16"/>
       <x:c r="D16"/>
@@ -5671,10 +6244,11 @@
     </x:row>
     <x:row r="17">
       <x:c r="A17" t="str">
-        <x:v>原采购总额</x:v>
+        <x:v>勾稽采购总额</x:v>
       </x:c>
       <x:c r="B17" s="90" t="n">
-        <x:v>9231.69</x:v>
+        <x:f>B15+B16</x:f>
+        <x:v>9402.880000000001</x:v>
       </x:c>
       <x:c r="C17"/>
       <x:c r="D17"/>
@@ -5684,17 +6258,30 @@
     </x:row>
     <x:row r="18">
       <x:c r="A18" t="str">
-        <x:v>差额</x:v>
+        <x:v>原采购总额</x:v>
       </x:c>
       <x:c r="B18" s="90" t="n">
-        <x:f>B16-B17</x:f>
-        <x:v>0</x:v>
+        <x:v>9402.88</x:v>
       </x:c>
       <x:c r="C18"/>
       <x:c r="D18"/>
       <x:c r="E18"/>
       <x:c r="F18"/>
       <x:c r="G18"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>差额</x:v>
+      </x:c>
+      <x:c r="B19" s="90" t="n">
+        <x:f>B17-B18</x:f>
+        <x:v>1.8189894035458565e-12</x:v>
+      </x:c>
+      <x:c r="C19"/>
+      <x:c r="D19"/>
+      <x:c r="E19"/>
+      <x:c r="F19"/>
+      <x:c r="G19"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
